--- a/【存储稳定性测试与数据一致性校验】测试用例.xlsx
+++ b/【存储稳定性测试与数据一致性校验】测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13100" tabRatio="460"/>
+    <workbookView windowWidth="27660" windowHeight="13140" tabRatio="460"/>
   </bookViews>
   <sheets>
     <sheet name="LBA工具测试用例" sheetId="6" r:id="rId1"/>
@@ -927,7 +927,7 @@
     </r>
   </si>
   <si>
-    <t>设置IO失败时重试</t>
+    <t>设置IO失败时重试&amp;静默错误检测</t>
   </si>
   <si>
     <t xml:space="preserve"> -r | --io-retry</t>
@@ -951,7 +951,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-r on</t>
+      <t>-R on</t>
     </r>
     <r>
       <rPr>
@@ -965,7 +965,19 @@
     </r>
   </si>
   <si>
-    <t>IO失败后重试</t>
+    <r>
+      <t>【重要功能】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IO失败后重试；指定区域和随机命中静默错误检测</t>
+    </r>
   </si>
   <si>
     <t>512K</t>
@@ -1258,7 +1270,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>-R 33</t>
+      <t>-r 33</t>
     </r>
     <r>
       <rPr>
@@ -7767,18 +7779,26 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3232F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3232F0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -7789,14 +7809,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7956,20 +7968,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7984,13 +7982,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="9"/>
+      <color theme="5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -8004,9 +8003,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF3232F0"/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -8017,6 +8021,14 @@
       <color rgb="FF3232F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF3232F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -8240,6 +8252,43 @@
       <left style="thick">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
       <right style="thick">
         <color auto="1"/>
       </right>
@@ -8271,6 +8320,72 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -8296,102 +8411,26 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
@@ -8433,17 +8472,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -8468,65 +8496,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thick">
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -8543,10 +8526,8 @@
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -8556,6 +8537,114 @@
       <right style="medium">
         <color auto="1"/>
       </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -8564,26 +8653,63 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thick">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thick">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -8593,21 +8719,51 @@
       <right style="thick">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thick">
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
       <right style="thick">
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -8618,57 +8774,22 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="thick">
         <color auto="1"/>
       </left>
       <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -8681,7 +8802,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -8696,153 +8817,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -8871,6 +8848,43 @@
     </border>
     <border>
       <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="medium">
@@ -8884,14 +8898,12 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thick">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -9170,376 +9182,376 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10322,11 +10334,11 @@
       <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
       <c r="H2" s="6" t="s">
         <v>5</v>
       </c>
@@ -10339,1914 +10351,1914 @@
       <c r="K2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="41"/>
-      <c r="M2" s="73" t="s">
+      <c r="L2" s="10"/>
+      <c r="M2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="81"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13"/>
     </row>
     <row r="3" ht="18.5" spans="1:17">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="22" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="43" t="s">
+      <c r="K3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="41"/>
-      <c r="M3" s="75"/>
-      <c r="Q3" s="82"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="23"/>
+      <c r="Q3" s="24"/>
     </row>
     <row r="4" ht="17.75" spans="1:17">
-      <c r="A4" s="7"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="42" t="s">
+      <c r="F4" s="19"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="44" t="s">
+      <c r="K4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="75"/>
-      <c r="Q4" s="82"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="23"/>
+      <c r="Q4" s="24"/>
     </row>
     <row r="5" ht="17.75" spans="1:17">
-      <c r="A5" s="7"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13" t="s">
+      <c r="A5" s="14"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="24" t="s">
+      <c r="F5" s="19"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="45" t="s">
+      <c r="I5" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="41"/>
-      <c r="M5" s="75"/>
-      <c r="Q5" s="82"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="23"/>
+      <c r="Q5" s="24"/>
     </row>
     <row r="6" ht="17.75" spans="1:17">
-      <c r="A6" s="7"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
+      <c r="A6" s="14"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="24" t="s">
+      <c r="F6" s="19"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="K6" s="47" t="s">
+      <c r="K6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="41"/>
-      <c r="M6" s="75"/>
-      <c r="Q6" s="82"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="23"/>
+      <c r="Q6" s="24"/>
     </row>
     <row r="7" ht="17.75" spans="1:17">
-      <c r="A7" s="7"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="19"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="45" t="s">
+      <c r="I7" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="46" t="s">
+      <c r="J7" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="K7" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="M7" s="75"/>
-      <c r="Q7" s="82"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="23"/>
+      <c r="Q7" s="24"/>
     </row>
     <row r="8" ht="17.75" spans="1:17">
-      <c r="A8" s="7"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="24" t="s">
+      <c r="F8" s="19"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="45" t="s">
+      <c r="I8" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="46" t="s">
+      <c r="J8" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="47" t="s">
+      <c r="K8" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="41"/>
-      <c r="M8" s="75"/>
-      <c r="Q8" s="82"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="23"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="17.75" spans="1:17">
-      <c r="A9" s="7"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13" t="s">
+      <c r="A9" s="14"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="24" t="s">
+      <c r="F9" s="19"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="46" t="s">
+      <c r="J9" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="K9" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="L9" s="41"/>
-      <c r="M9" s="75"/>
-      <c r="Q9" s="82"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="23"/>
+      <c r="Q9" s="24"/>
     </row>
     <row r="10" ht="17.75" spans="1:17">
-      <c r="A10" s="7"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
+      <c r="A10" s="14"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="24" t="s">
+      <c r="F10" s="19"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="45" t="s">
+      <c r="I10" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="41"/>
-      <c r="M10" s="75"/>
-      <c r="Q10" s="82"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="23"/>
+      <c r="Q10" s="24"/>
     </row>
     <row r="11" ht="17.75" spans="1:17">
-      <c r="A11" s="7"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="14" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="24" t="s">
+      <c r="F11" s="36"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="45" t="s">
+      <c r="I11" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="46" t="s">
+      <c r="J11" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="L11" s="41"/>
-      <c r="M11" s="75"/>
-      <c r="Q11" s="82"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="23"/>
+      <c r="Q11" s="24"/>
     </row>
     <row r="12" ht="17.75" spans="1:17">
-      <c r="A12" s="7"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="28"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="24" t="s">
+      <c r="F12" s="38"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="45" t="s">
+      <c r="I12" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="K12" s="47" t="s">
+      <c r="K12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="L12" s="41"/>
-      <c r="M12" s="75"/>
-      <c r="Q12" s="82"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="23"/>
+      <c r="Q12" s="24"/>
     </row>
     <row r="13" ht="17.75" spans="1:17">
-      <c r="A13" s="7"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13" t="s">
+      <c r="A13" s="14"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="29" t="s">
+      <c r="F13" s="19"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="44" t="s">
+      <c r="K13" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="75"/>
-      <c r="Q13" s="82"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="23"/>
+      <c r="Q13" s="24"/>
     </row>
     <row r="14" ht="17.75" spans="1:17">
-      <c r="A14" s="7"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13" t="s">
+      <c r="A14" s="14"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="46" t="s">
+      <c r="F14" s="19"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="44" t="s">
+      <c r="K14" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="75"/>
-      <c r="Q14" s="82"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="23"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" ht="17.75" spans="1:17">
-      <c r="A15" s="7"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="46" t="s">
+      <c r="F15" s="19"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="K15" s="49" t="s">
+      <c r="K15" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="L15" s="41"/>
-      <c r="M15" s="75"/>
-      <c r="Q15" s="82"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="23"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" ht="17.75" spans="1:17">
-      <c r="A16" s="7"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="29" t="s">
+      <c r="F16" s="19"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="39" t="s">
         <v>83</v>
       </c>
-      <c r="I16" s="48" t="s">
+      <c r="I16" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="J16" s="46" t="s">
+      <c r="J16" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="K16" s="50" t="s">
+      <c r="K16" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="75"/>
-      <c r="Q16" s="82"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="23"/>
+      <c r="Q16" s="24"/>
     </row>
     <row r="17" ht="17.75" spans="1:17">
-      <c r="A17" s="7"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="46" t="s">
+      <c r="F17" s="19"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="L17" s="41"/>
-      <c r="M17" s="75"/>
-      <c r="Q17" s="82"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="23"/>
+      <c r="Q17" s="24"/>
     </row>
     <row r="18" ht="17.75" spans="1:17">
-      <c r="A18" s="7"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="23" t="s">
+      <c r="F18" s="19"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="I18" s="48" t="s">
+      <c r="I18" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="J18" s="46" t="s">
+      <c r="J18" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K18" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="75"/>
-      <c r="Q18" s="82"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="23"/>
+      <c r="Q18" s="24"/>
     </row>
     <row r="19" ht="17.75" spans="1:17">
-      <c r="A19" s="7"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="46" t="s">
+      <c r="F19" s="19"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="K19" s="49" t="s">
+      <c r="K19" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="75"/>
-      <c r="Q19" s="82"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="23"/>
+      <c r="Q19" s="24"/>
     </row>
     <row r="20" ht="17.75" spans="1:17">
-      <c r="A20" s="7"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="14" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="F20" s="26"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="46" t="s">
+      <c r="F20" s="36"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="K20" s="49" t="s">
+      <c r="K20" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="L20" s="41"/>
-      <c r="M20" s="75"/>
-      <c r="Q20" s="82"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="23"/>
+      <c r="Q20" s="24"/>
     </row>
     <row r="21" ht="17.75" spans="1:17">
-      <c r="A21" s="7"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="F21" s="28"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="24" t="s">
+      <c r="F21" s="38"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="I21" s="45" t="s">
+      <c r="I21" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="J21" s="46" t="s">
+      <c r="J21" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="44" t="s">
+      <c r="K21" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="L21" s="41"/>
-      <c r="M21" s="75"/>
-      <c r="Q21" s="82"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="23"/>
+      <c r="Q21" s="24"/>
     </row>
     <row r="22" ht="17.75" spans="1:17">
-      <c r="A22" s="7"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13" t="s">
+      <c r="A22" s="14"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="24" t="s">
+      <c r="F22" s="19"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="I22" s="45" t="s">
+      <c r="I22" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="J22" s="46" t="s">
+      <c r="J22" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="L22" s="41"/>
-      <c r="M22" s="75"/>
-      <c r="Q22" s="82"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="23"/>
+      <c r="Q22" s="24"/>
     </row>
     <row r="23" ht="17.75" spans="1:17">
-      <c r="A23" s="7"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="24" t="s">
+      <c r="F23" s="19"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="I23" s="45" t="s">
+      <c r="I23" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="J23" s="46" t="s">
+      <c r="J23" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="K23" s="44" t="s">
+      <c r="K23" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="L23" s="41"/>
-      <c r="M23" s="75"/>
-      <c r="Q23" s="82"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="23"/>
+      <c r="Q23" s="24"/>
     </row>
     <row r="24" ht="17.75" spans="1:17">
-      <c r="A24" s="7"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="29" t="s">
+      <c r="F24" s="19"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="I24" s="48" t="s">
+      <c r="I24" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="J24" s="46" t="s">
+      <c r="J24" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="K24" s="47" t="s">
+      <c r="K24" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="L24" s="41"/>
-      <c r="M24" s="75"/>
-      <c r="Q24" s="82"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="23"/>
+      <c r="Q24" s="24"/>
     </row>
     <row r="25" ht="17.75" spans="1:17">
-      <c r="A25" s="7"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="46" t="s">
+      <c r="F25" s="19"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="L25" s="41"/>
-      <c r="M25" s="75"/>
-      <c r="Q25" s="82"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="23"/>
+      <c r="Q25" s="24"/>
     </row>
     <row r="26" ht="19.1" spans="1:17">
-      <c r="A26" s="7"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13" t="s">
+      <c r="A26" s="14"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="21"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="46" t="s">
+      <c r="F26" s="19"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="K26" s="47" t="s">
+      <c r="K26" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="L26" s="41"/>
-      <c r="M26" s="76" t="s">
+      <c r="L26" s="10"/>
+      <c r="M26" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="N26" s="77"/>
-      <c r="O26" s="77"/>
-      <c r="P26" s="77"/>
-      <c r="Q26" s="83"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="47"/>
+      <c r="Q26" s="48"/>
     </row>
     <row r="27" ht="18.5" spans="1:17">
-      <c r="A27" s="7"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13" t="s">
+      <c r="A27" s="14"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="46" t="s">
+      <c r="F27" s="19"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="L27" s="41"/>
-      <c r="M27" s="22" t="s">
+      <c r="L27" s="10"/>
+      <c r="M27" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="N27" s="78" t="s">
+      <c r="N27" s="49" t="s">
         <v>132</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="O27" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="84"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="51"/>
     </row>
     <row r="28" ht="17.75" spans="1:17">
-      <c r="A28" s="7"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13" t="s">
+      <c r="A28" s="14"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="46" t="s">
+      <c r="F28" s="19"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="L28" s="41"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="80" t="s">
+      <c r="L28" s="10"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="P28" s="80"/>
-      <c r="Q28" s="84"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="51"/>
     </row>
     <row r="29" ht="17.75" spans="1:17">
-      <c r="A29" s="7"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="14" t="s">
+      <c r="A29" s="14"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="26"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="51" t="s">
+      <c r="F29" s="36"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="K29" s="47" t="s">
+      <c r="K29" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L29" s="41"/>
-      <c r="M29" s="23"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="80" t="s">
+      <c r="L29" s="10"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="84"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="51"/>
     </row>
     <row r="30" ht="17.75" spans="1:17">
-      <c r="A30" s="7"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="15" t="s">
+      <c r="A30" s="14"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="53" t="s">
+      <c r="F30" s="38"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="56" t="s">
         <v>144</v>
       </c>
-      <c r="K30" s="54" t="s">
+      <c r="K30" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="L30" s="41"/>
-      <c r="M30" s="23"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="80" t="s">
+      <c r="L30" s="10"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="P30" s="80"/>
-      <c r="Q30" s="84"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="51"/>
     </row>
     <row r="31" ht="17.55" spans="1:17">
-      <c r="A31" s="7"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="13" t="s">
+      <c r="A31" s="14"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="80" t="s">
+      <c r="F31" s="19"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="P31" s="80"/>
-      <c r="Q31" s="84"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="51"/>
     </row>
     <row r="32" ht="18.3" spans="1:17">
-      <c r="A32" s="7"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13" t="s">
+      <c r="A32" s="14"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="21"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="34" t="s">
+      <c r="F32" s="19"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="I32" s="55" t="s">
+      <c r="I32" s="60" t="s">
         <v>151</v>
       </c>
-      <c r="J32" s="55"/>
-      <c r="K32" s="34" t="s">
+      <c r="J32" s="60"/>
+      <c r="K32" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="41"/>
-      <c r="M32" s="23"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="80" t="s">
+      <c r="L32" s="10"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="P32" s="80"/>
-      <c r="Q32" s="84"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="51"/>
     </row>
     <row r="33" ht="17.55" spans="1:17">
-      <c r="A33" s="7"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13" t="s">
+      <c r="A33" s="14"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F33" s="21"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="35" t="s">
+      <c r="F33" s="19"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I33" s="56" t="s">
+      <c r="I33" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="J33" s="57"/>
-      <c r="K33" s="58" t="s">
+      <c r="J33" s="63"/>
+      <c r="K33" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="L33" s="41"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="80" t="s">
+      <c r="L33" s="10"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="P33" s="80"/>
-      <c r="Q33" s="84"/>
+      <c r="P33" s="52"/>
+      <c r="Q33" s="51"/>
     </row>
     <row r="34" ht="17.55" spans="1:17">
-      <c r="A34" s="7"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="14" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="F34" s="26"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="36" t="s">
+      <c r="F34" s="36"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="I34" s="59" t="s">
+      <c r="I34" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="J34" s="60"/>
-      <c r="K34" s="61" t="s">
+      <c r="J34" s="67"/>
+      <c r="K34" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="L34" s="41"/>
-      <c r="M34" s="23"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="80" t="s">
+      <c r="L34" s="10"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="P34" s="80"/>
-      <c r="Q34" s="84"/>
+      <c r="P34" s="52"/>
+      <c r="Q34" s="51"/>
     </row>
     <row r="35" ht="18.3" spans="1:17">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="69" t="s">
         <v>163</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="36" t="s">
+      <c r="F35" s="38"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="65" t="s">
         <v>166</v>
       </c>
-      <c r="I35" s="59" t="s">
+      <c r="I35" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="J35" s="60"/>
-      <c r="K35" s="58" t="s">
+      <c r="J35" s="67"/>
+      <c r="K35" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L35" s="41"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="12" t="s">
+      <c r="L35" s="10"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="O35" s="80" t="s">
+      <c r="O35" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="P35" s="80"/>
-      <c r="Q35" s="84"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="51"/>
     </row>
     <row r="36" ht="17.55" spans="1:17">
-      <c r="A36" s="7"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13" t="s">
+      <c r="A36" s="14"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="F36" s="21"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="36" t="s">
+      <c r="F36" s="19"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="I36" s="59" t="s">
+      <c r="I36" s="66" t="s">
         <v>173</v>
       </c>
-      <c r="J36" s="60"/>
-      <c r="K36" s="61" t="s">
+      <c r="J36" s="67"/>
+      <c r="K36" s="68" t="s">
         <v>174</v>
       </c>
-      <c r="L36" s="41"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="80" t="s">
+      <c r="L36" s="10"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="52" t="s">
         <v>175</v>
       </c>
-      <c r="P36" s="80"/>
-      <c r="Q36" s="84"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="51"/>
     </row>
     <row r="37" ht="17.55" spans="1:17">
-      <c r="A37" s="7"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13" t="s">
+      <c r="A37" s="14"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="21"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="36" t="s">
+      <c r="F37" s="19"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="65" t="s">
         <v>177</v>
       </c>
-      <c r="I37" s="59" t="s">
+      <c r="I37" s="66" t="s">
         <v>178</v>
       </c>
-      <c r="J37" s="60"/>
-      <c r="K37" s="61" t="s">
+      <c r="J37" s="67"/>
+      <c r="K37" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="L37" s="41"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="12" t="s">
+      <c r="L37" s="10"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="O37" s="80" t="s">
+      <c r="O37" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="P37" s="80"/>
-      <c r="Q37" s="84"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="51"/>
     </row>
     <row r="38" ht="17.55" spans="1:17">
-      <c r="A38" s="7"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13" t="s">
+      <c r="A38" s="14"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="F38" s="21"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="36" t="s">
+      <c r="F38" s="19"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="I38" s="59" t="s">
+      <c r="I38" s="66" t="s">
         <v>184</v>
       </c>
-      <c r="J38" s="60"/>
-      <c r="K38" s="58" t="s">
+      <c r="J38" s="67"/>
+      <c r="K38" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L38" s="41"/>
-      <c r="M38" s="23"/>
-      <c r="N38" s="12"/>
-      <c r="O38" s="80" t="s">
+      <c r="L38" s="10"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="52" t="s">
         <v>185</v>
       </c>
-      <c r="P38" s="80"/>
-      <c r="Q38" s="84"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="51"/>
     </row>
     <row r="39" ht="17.55" spans="1:17">
-      <c r="A39" s="7"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="F39" s="21"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="36" t="s">
+      <c r="F39" s="19"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="65" t="s">
         <v>187</v>
       </c>
-      <c r="I39" s="59" t="s">
+      <c r="I39" s="66" t="s">
         <v>188</v>
       </c>
-      <c r="J39" s="60"/>
-      <c r="K39" s="61" t="s">
+      <c r="J39" s="67"/>
+      <c r="K39" s="68" t="s">
         <v>189</v>
       </c>
-      <c r="L39" s="41"/>
-      <c r="M39" s="23" t="s">
+      <c r="L39" s="10"/>
+      <c r="M39" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="N39" s="12" t="s">
+      <c r="N39" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="O39" s="80" t="s">
+      <c r="O39" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="P39" s="80"/>
-      <c r="Q39" s="84"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="51"/>
     </row>
     <row r="40" ht="17.55" spans="1:17">
-      <c r="A40" s="7"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="F40" s="21"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="36" t="s">
+      <c r="F40" s="19"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="I40" s="59" t="s">
+      <c r="I40" s="66" t="s">
         <v>195</v>
       </c>
-      <c r="J40" s="60"/>
-      <c r="K40" s="61" t="s">
+      <c r="J40" s="67"/>
+      <c r="K40" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="L40" s="41"/>
-      <c r="M40" s="23"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="80" t="s">
+      <c r="L40" s="10"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="P40" s="80"/>
-      <c r="Q40" s="84"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="51"/>
     </row>
     <row r="41" ht="17.55" spans="1:17">
-      <c r="A41" s="7"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13" t="s">
+      <c r="A41" s="14"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="F41" s="21"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="36" t="s">
+      <c r="F41" s="19"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="65" t="s">
         <v>198</v>
       </c>
-      <c r="I41" s="59" t="s">
+      <c r="I41" s="66" t="s">
         <v>199</v>
       </c>
-      <c r="J41" s="60"/>
-      <c r="K41" s="58" t="s">
+      <c r="J41" s="67"/>
+      <c r="K41" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L41" s="41"/>
-      <c r="M41" s="23"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="80" t="s">
+      <c r="L41" s="10"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="P41" s="80"/>
-      <c r="Q41" s="84"/>
+      <c r="P41" s="52"/>
+      <c r="Q41" s="51"/>
     </row>
     <row r="42" ht="17.55" spans="1:17">
-      <c r="A42" s="7"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13" t="s">
+      <c r="A42" s="14"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F42" s="21"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="36" t="s">
+      <c r="F42" s="19"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="65" t="s">
         <v>202</v>
       </c>
-      <c r="I42" s="59" t="s">
+      <c r="I42" s="66" t="s">
         <v>203</v>
       </c>
-      <c r="J42" s="60"/>
-      <c r="K42" s="58" t="s">
+      <c r="J42" s="67"/>
+      <c r="K42" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="L42" s="41"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="80" t="s">
+      <c r="L42" s="10"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="52" t="s">
         <v>205</v>
       </c>
-      <c r="P42" s="80"/>
-      <c r="Q42" s="84"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="51"/>
     </row>
     <row r="43" ht="17.55" spans="1:17">
-      <c r="A43" s="7"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="14" t="s">
+      <c r="A43" s="14"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="F43" s="26"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="36" t="s">
+      <c r="F43" s="36"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="I43" s="59" t="s">
+      <c r="I43" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="J43" s="60"/>
-      <c r="K43" s="61" t="s">
+      <c r="J43" s="67"/>
+      <c r="K43" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="L43" s="41"/>
-      <c r="M43" s="23"/>
-      <c r="N43" s="12" t="s">
+      <c r="L43" s="10"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="O43" s="80" t="s">
+      <c r="O43" s="52" t="s">
         <v>211</v>
       </c>
-      <c r="P43" s="80"/>
-      <c r="Q43" s="84"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="51"/>
     </row>
     <row r="44" ht="17.55" spans="1:17">
-      <c r="A44" s="7"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12" t="s">
+      <c r="A44" s="14"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="E44" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="F44" s="28"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="37" t="s">
+      <c r="F44" s="38"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="70" t="s">
         <v>213</v>
       </c>
-      <c r="I44" s="62" t="s">
+      <c r="I44" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="J44" s="63"/>
-      <c r="K44" s="64" t="s">
+      <c r="J44" s="72"/>
+      <c r="K44" s="73" t="s">
         <v>215</v>
       </c>
-      <c r="L44" s="41"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="80" t="s">
+      <c r="L44" s="10"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="P44" s="80"/>
-      <c r="Q44" s="84"/>
+      <c r="P44" s="52"/>
+      <c r="Q44" s="51"/>
     </row>
     <row r="45" ht="17.55" spans="1:17">
-      <c r="A45" s="7"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="13" t="s">
+      <c r="A45" s="14"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="F45" s="21"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="35" t="s">
+      <c r="F45" s="19"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="61" t="s">
         <v>218</v>
       </c>
-      <c r="I45" s="56" t="s">
+      <c r="I45" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="J45" s="57"/>
-      <c r="K45" s="58" t="s">
+      <c r="J45" s="63"/>
+      <c r="K45" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="L45" s="41"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="80" t="s">
+      <c r="L45" s="10"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="52" t="s">
         <v>221</v>
       </c>
-      <c r="P45" s="80"/>
-      <c r="Q45" s="84"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="51"/>
     </row>
     <row r="46" ht="17.55" spans="1:17">
-      <c r="A46" s="7"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13" t="s">
+      <c r="A46" s="14"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F46" s="21"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="36" t="s">
+      <c r="F46" s="19"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="65" t="s">
         <v>223</v>
       </c>
-      <c r="I46" s="59" t="s">
+      <c r="I46" s="66" t="s">
         <v>224</v>
       </c>
-      <c r="J46" s="60"/>
-      <c r="K46" s="61" t="s">
+      <c r="J46" s="67"/>
+      <c r="K46" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="L46" s="41"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="80" t="s">
+      <c r="L46" s="10"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="P46" s="80"/>
-      <c r="Q46" s="84"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="51"/>
     </row>
     <row r="47" ht="17.55" spans="1:17">
-      <c r="A47" s="7"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13" t="s">
+      <c r="A47" s="14"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F47" s="21"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="36" t="s">
+      <c r="F47" s="19"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="I47" s="59" t="s">
+      <c r="I47" s="66" t="s">
         <v>228</v>
       </c>
-      <c r="J47" s="60"/>
-      <c r="K47" s="58" t="s">
+      <c r="J47" s="67"/>
+      <c r="K47" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L47" s="41"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="80" t="s">
+      <c r="L47" s="10"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="P47" s="80"/>
-      <c r="Q47" s="84"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="51"/>
     </row>
     <row r="48" ht="17.55" spans="1:17">
-      <c r="A48" s="7"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="13" t="s">
+      <c r="A48" s="14"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="F48" s="21"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="36" t="s">
+      <c r="F48" s="19"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="I48" s="59" t="s">
+      <c r="I48" s="66" t="s">
         <v>232</v>
       </c>
-      <c r="J48" s="60"/>
-      <c r="K48" s="61" t="s">
+      <c r="J48" s="67"/>
+      <c r="K48" s="68" t="s">
         <v>233</v>
       </c>
-      <c r="L48" s="41"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="12" t="s">
+      <c r="L48" s="10"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="O48" s="80" t="s">
+      <c r="O48" s="52" t="s">
         <v>235</v>
       </c>
-      <c r="P48" s="80"/>
-      <c r="Q48" s="84"/>
+      <c r="P48" s="52"/>
+      <c r="Q48" s="51"/>
     </row>
     <row r="49" ht="17.55" spans="1:17">
-      <c r="A49" s="7"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="13" t="s">
+      <c r="A49" s="14"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="F49" s="21"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="36" t="s">
+      <c r="F49" s="19"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="65" t="s">
         <v>237</v>
       </c>
-      <c r="I49" s="59" t="s">
+      <c r="I49" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="J49" s="60"/>
-      <c r="K49" s="61" t="s">
+      <c r="J49" s="67"/>
+      <c r="K49" s="68" t="s">
         <v>179</v>
       </c>
-      <c r="L49" s="41"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="80" t="s">
+      <c r="L49" s="10"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="26"/>
+      <c r="O49" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="P49" s="80"/>
-      <c r="Q49" s="84"/>
+      <c r="P49" s="52"/>
+      <c r="Q49" s="51"/>
     </row>
     <row r="50" ht="17.55" spans="1:17">
-      <c r="A50" s="7"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="13" t="s">
+      <c r="A50" s="14"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="F50" s="21"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="36" t="s">
+      <c r="F50" s="19"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="65" t="s">
         <v>241</v>
       </c>
-      <c r="I50" s="59" t="s">
+      <c r="I50" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="J50" s="60"/>
-      <c r="K50" s="58" t="s">
+      <c r="J50" s="67"/>
+      <c r="K50" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L50" s="41"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="80" t="s">
+      <c r="L50" s="10"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="52" t="s">
         <v>243</v>
       </c>
-      <c r="P50" s="80"/>
-      <c r="Q50" s="84"/>
+      <c r="P50" s="52"/>
+      <c r="Q50" s="51"/>
     </row>
     <row r="51" ht="17.55" spans="1:17">
-      <c r="A51" s="7"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="13" t="s">
+      <c r="A51" s="14"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="F51" s="21"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="36" t="s">
+      <c r="F51" s="19"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="65" t="s">
         <v>245</v>
       </c>
-      <c r="I51" s="59" t="s">
+      <c r="I51" s="66" t="s">
         <v>246</v>
       </c>
-      <c r="J51" s="60"/>
-      <c r="K51" s="61" t="s">
+      <c r="J51" s="67"/>
+      <c r="K51" s="68" t="s">
         <v>247</v>
       </c>
-      <c r="L51" s="41"/>
-      <c r="M51" s="23"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="80" t="s">
+      <c r="L51" s="10"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="26"/>
+      <c r="O51" s="52" t="s">
         <v>248</v>
       </c>
-      <c r="P51" s="80"/>
-      <c r="Q51" s="84"/>
+      <c r="P51" s="52"/>
+      <c r="Q51" s="51"/>
     </row>
     <row r="52" ht="17.55" spans="1:17">
-      <c r="A52" s="7"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="14" t="s">
+      <c r="A52" s="14"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="25" t="s">
+      <c r="E52" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="F52" s="26"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="36" t="s">
+      <c r="F52" s="36"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="65" t="s">
         <v>250</v>
       </c>
-      <c r="I52" s="59" t="s">
+      <c r="I52" s="66" t="s">
         <v>251</v>
       </c>
-      <c r="J52" s="60"/>
-      <c r="K52" s="61" t="s">
+      <c r="J52" s="67"/>
+      <c r="K52" s="68" t="s">
         <v>161</v>
       </c>
-      <c r="L52" s="41"/>
-      <c r="M52" s="23"/>
-      <c r="N52" s="45" t="s">
+      <c r="L52" s="10"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="O52" s="80" t="s">
+      <c r="O52" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="P52" s="80"/>
-      <c r="Q52" s="84"/>
+      <c r="P52" s="52"/>
+      <c r="Q52" s="51"/>
     </row>
     <row r="53" ht="17.55" spans="1:17">
-      <c r="A53" s="7"/>
-      <c r="B53" s="11" t="s">
+      <c r="A53" s="14"/>
+      <c r="B53" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="45" t="s">
         <v>255</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="27" t="s">
+      <c r="E53" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="36" t="s">
+      <c r="F53" s="38"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="65" t="s">
         <v>257</v>
       </c>
-      <c r="I53" s="59" t="s">
+      <c r="I53" s="66" t="s">
         <v>258</v>
       </c>
-      <c r="J53" s="60"/>
-      <c r="K53" s="58" t="s">
+      <c r="J53" s="67"/>
+      <c r="K53" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="L53" s="41"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="12" t="s">
+      <c r="L53" s="10"/>
+      <c r="M53" s="28"/>
+      <c r="N53" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="O53" s="80" t="s">
+      <c r="O53" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="P53" s="80"/>
-      <c r="Q53" s="84"/>
+      <c r="P53" s="52"/>
+      <c r="Q53" s="51"/>
     </row>
     <row r="54" ht="17.55" spans="1:17">
-      <c r="A54" s="7"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="13" t="s">
+      <c r="A54" s="14"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="F54" s="21"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="36" t="s">
+      <c r="F54" s="19"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="65" t="s">
         <v>262</v>
       </c>
-      <c r="I54" s="59" t="s">
+      <c r="I54" s="66" t="s">
         <v>263</v>
       </c>
-      <c r="J54" s="60"/>
-      <c r="K54" s="58" t="s">
+      <c r="J54" s="67"/>
+      <c r="K54" s="64" t="s">
         <v>264</v>
       </c>
-      <c r="L54" s="41"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="12"/>
-      <c r="O54" s="80" t="s">
+      <c r="L54" s="10"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="26"/>
+      <c r="O54" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="84"/>
+      <c r="P54" s="52"/>
+      <c r="Q54" s="51"/>
     </row>
     <row r="55" ht="17.55" spans="1:17">
-      <c r="A55" s="7"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="13" t="s">
+      <c r="A55" s="14"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="F55" s="21"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="36" t="s">
+      <c r="F55" s="19"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="65" t="s">
         <v>267</v>
       </c>
-      <c r="I55" s="59" t="s">
+      <c r="I55" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="J55" s="60"/>
-      <c r="K55" s="61" t="s">
+      <c r="J55" s="67"/>
+      <c r="K55" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="L55" s="41"/>
-      <c r="M55" s="23" t="s">
+      <c r="L55" s="10"/>
+      <c r="M55" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="N55" s="45" t="s">
+      <c r="N55" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="O55" s="80" t="s">
+      <c r="O55" s="52" t="s">
         <v>271</v>
       </c>
-      <c r="P55" s="80"/>
-      <c r="Q55" s="84"/>
+      <c r="P55" s="52"/>
+      <c r="Q55" s="51"/>
     </row>
     <row r="56" ht="17.55" spans="1:17">
-      <c r="A56" s="7"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="13" t="s">
+      <c r="A56" s="14"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="F56" s="21"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="37" t="s">
+      <c r="F56" s="19"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="70" t="s">
         <v>273</v>
       </c>
-      <c r="I56" s="62" t="s">
+      <c r="I56" s="71" t="s">
         <v>274</v>
       </c>
-      <c r="J56" s="63"/>
-      <c r="K56" s="64" t="s">
+      <c r="J56" s="72"/>
+      <c r="K56" s="73" t="s">
         <v>215</v>
       </c>
-      <c r="L56" s="41"/>
-      <c r="M56" s="23"/>
-      <c r="N56" s="12" t="s">
+      <c r="L56" s="10"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="O56" s="80" t="s">
+      <c r="O56" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="P56" s="80"/>
-      <c r="Q56" s="84"/>
+      <c r="P56" s="52"/>
+      <c r="Q56" s="51"/>
     </row>
     <row r="57" ht="17.55" spans="1:17">
-      <c r="A57" s="7"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13" t="s">
+      <c r="A57" s="14"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="F57" s="21"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="35" t="s">
+      <c r="F57" s="19"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="61" t="s">
         <v>278</v>
       </c>
-      <c r="I57" s="56" t="s">
+      <c r="I57" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="J57" s="57"/>
-      <c r="K57" s="58" t="s">
+      <c r="J57" s="63"/>
+      <c r="K57" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="L57" s="41"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="12"/>
-      <c r="O57" s="80" t="s">
+      <c r="L57" s="10"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="P57" s="80"/>
-      <c r="Q57" s="84"/>
+      <c r="P57" s="52"/>
+      <c r="Q57" s="51"/>
     </row>
     <row r="58" ht="17.55" spans="1:17">
-      <c r="A58" s="7"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13" t="s">
+      <c r="A58" s="14"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="F58" s="21"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="36" t="s">
+      <c r="F58" s="19"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="65" t="s">
         <v>283</v>
       </c>
-      <c r="I58" s="59" t="s">
+      <c r="I58" s="66" t="s">
         <v>284</v>
       </c>
-      <c r="J58" s="60"/>
-      <c r="K58" s="58" t="s">
+      <c r="J58" s="67"/>
+      <c r="K58" s="64" t="s">
         <v>285</v>
       </c>
-      <c r="L58" s="41"/>
-      <c r="M58" s="23"/>
-      <c r="N58" s="12"/>
-      <c r="O58" s="80" t="s">
+      <c r="L58" s="10"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="52" t="s">
         <v>286</v>
       </c>
-      <c r="P58" s="80"/>
-      <c r="Q58" s="84"/>
+      <c r="P58" s="52"/>
+      <c r="Q58" s="51"/>
     </row>
     <row r="59" ht="17.55" spans="1:17">
-      <c r="A59" s="7"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13" t="s">
+      <c r="A59" s="14"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="F59" s="21"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="36" t="s">
+      <c r="F59" s="19"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="I59" s="59" t="s">
+      <c r="I59" s="66" t="s">
         <v>289</v>
       </c>
-      <c r="J59" s="60"/>
-      <c r="K59" s="58" t="s">
+      <c r="J59" s="67"/>
+      <c r="K59" s="64" t="s">
         <v>290</v>
       </c>
-      <c r="L59" s="41"/>
-      <c r="M59" s="23"/>
-      <c r="N59" s="12"/>
-      <c r="O59" s="80" t="s">
+      <c r="L59" s="10"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="52" t="s">
         <v>291</v>
       </c>
-      <c r="P59" s="80"/>
-      <c r="Q59" s="84"/>
+      <c r="P59" s="52"/>
+      <c r="Q59" s="51"/>
     </row>
     <row r="60" ht="17.55" spans="1:17">
-      <c r="A60" s="7"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13" t="s">
+      <c r="A60" s="14"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="F60" s="21"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="36" t="s">
+      <c r="F60" s="19"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="65" t="s">
         <v>293</v>
       </c>
-      <c r="I60" s="59" t="s">
+      <c r="I60" s="66" t="s">
         <v>294</v>
       </c>
-      <c r="J60" s="60"/>
-      <c r="K60" s="61" t="s">
+      <c r="J60" s="67"/>
+      <c r="K60" s="68" t="s">
         <v>295</v>
       </c>
-      <c r="L60" s="41"/>
-      <c r="M60" s="23" t="s">
+      <c r="L60" s="10"/>
+      <c r="M60" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="N60" s="12" t="s">
+      <c r="N60" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="O60" s="80" t="s">
+      <c r="O60" s="52" t="s">
         <v>298</v>
       </c>
-      <c r="P60" s="80"/>
-      <c r="Q60" s="84"/>
+      <c r="P60" s="52"/>
+      <c r="Q60" s="51"/>
     </row>
     <row r="61" ht="17.55" spans="1:17">
-      <c r="A61" s="7"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="14" t="s">
+      <c r="A61" s="14"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="E61" s="25" t="s">
+      <c r="E61" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="36" t="s">
+      <c r="F61" s="36"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="65" t="s">
         <v>300</v>
       </c>
-      <c r="I61" s="59" t="s">
+      <c r="I61" s="66" t="s">
         <v>301</v>
       </c>
-      <c r="J61" s="60"/>
-      <c r="K61" s="61" t="s">
+      <c r="J61" s="67"/>
+      <c r="K61" s="68" t="s">
         <v>302</v>
       </c>
-      <c r="L61" s="41"/>
-      <c r="M61" s="23"/>
-      <c r="N61" s="12"/>
-      <c r="O61" s="80" t="s">
+      <c r="L61" s="10"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="52" t="s">
         <v>303</v>
       </c>
-      <c r="P61" s="80"/>
-      <c r="Q61" s="84"/>
+      <c r="P61" s="52"/>
+      <c r="Q61" s="51"/>
     </row>
     <row r="62" ht="17.55" spans="1:17">
-      <c r="A62" s="7"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="15" t="s">
+      <c r="A62" s="14"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="45" t="s">
         <v>304</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="E62" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="F62" s="28"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="38" t="s">
+      <c r="F62" s="38"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="74" t="s">
         <v>306</v>
       </c>
-      <c r="I62" s="65" t="s">
+      <c r="I62" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="J62" s="66"/>
-      <c r="K62" s="67" t="s">
+      <c r="J62" s="76"/>
+      <c r="K62" s="77" t="s">
         <v>308</v>
       </c>
-      <c r="L62" s="41"/>
-      <c r="M62" s="23"/>
-      <c r="N62" s="12"/>
-      <c r="O62" s="80" t="s">
+      <c r="L62" s="10"/>
+      <c r="M62" s="28"/>
+      <c r="N62" s="26"/>
+      <c r="O62" s="52" t="s">
         <v>309</v>
       </c>
-      <c r="P62" s="80"/>
-      <c r="Q62" s="84"/>
+      <c r="P62" s="52"/>
+      <c r="Q62" s="51"/>
     </row>
     <row r="63" ht="17.55" spans="1:17">
-      <c r="A63" s="7"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="13" t="s">
+      <c r="A63" s="14"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="F63" s="21"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="39" t="s">
+      <c r="F63" s="19"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="78" t="s">
         <v>311</v>
       </c>
-      <c r="I63" s="68" t="s">
+      <c r="I63" s="79" t="s">
         <v>312</v>
       </c>
-      <c r="J63" s="69"/>
-      <c r="K63" s="70" t="s">
+      <c r="J63" s="80"/>
+      <c r="K63" s="81" t="s">
         <v>313</v>
       </c>
-      <c r="L63" s="41"/>
-      <c r="M63" s="23"/>
-      <c r="N63" s="12"/>
-      <c r="O63" s="80" t="s">
+      <c r="L63" s="10"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="P63" s="80"/>
-      <c r="Q63" s="84"/>
+      <c r="P63" s="52"/>
+      <c r="Q63" s="51"/>
     </row>
     <row r="64" ht="17.55" spans="1:17">
-      <c r="A64" s="7"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="13" t="s">
+      <c r="A64" s="14"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="F64" s="21"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="71" t="s">
+      <c r="F64" s="19"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="82"/>
+      <c r="I64" s="83" t="s">
         <v>316</v>
       </c>
-      <c r="J64" s="72"/>
-      <c r="K64" s="61" t="s">
+      <c r="J64" s="84"/>
+      <c r="K64" s="68" t="s">
         <v>317</v>
       </c>
-      <c r="L64" s="41"/>
-      <c r="M64" s="23" t="s">
+      <c r="L64" s="10"/>
+      <c r="M64" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="N64" s="12" t="s">
+      <c r="N64" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="O64" s="80" t="s">
+      <c r="O64" s="52" t="s">
         <v>320</v>
       </c>
-      <c r="P64" s="80"/>
-      <c r="Q64" s="84"/>
+      <c r="P64" s="52"/>
+      <c r="Q64" s="51"/>
     </row>
     <row r="65" ht="17.55" spans="1:17">
-      <c r="A65" s="7"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13" t="s">
+      <c r="A65" s="14"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="F65" s="21"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="40" t="s">
+      <c r="F65" s="19"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="82" t="s">
         <v>322</v>
       </c>
-      <c r="I65" s="71" t="s">
+      <c r="I65" s="83" t="s">
         <v>312</v>
       </c>
-      <c r="J65" s="72"/>
-      <c r="K65" s="61" t="s">
+      <c r="J65" s="84"/>
+      <c r="K65" s="68" t="s">
         <v>313</v>
       </c>
-      <c r="L65" s="41"/>
-      <c r="M65" s="23"/>
-      <c r="N65" s="12"/>
-      <c r="O65" s="80" t="s">
+      <c r="L65" s="10"/>
+      <c r="M65" s="28"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="52" t="s">
         <v>323</v>
       </c>
-      <c r="P65" s="80"/>
-      <c r="Q65" s="84"/>
+      <c r="P65" s="52"/>
+      <c r="Q65" s="51"/>
     </row>
     <row r="66" ht="17.55" spans="1:17">
       <c r="A66" s="85"/>
@@ -12255,369 +12267,369 @@
       <c r="D66" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="E66" s="92" t="s">
+      <c r="E66" s="89" t="s">
         <v>324</v>
       </c>
-      <c r="F66" s="93"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="94"/>
-      <c r="I66" s="101" t="s">
+      <c r="F66" s="90"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="91"/>
+      <c r="I66" s="92" t="s">
         <v>325</v>
       </c>
-      <c r="J66" s="102"/>
-      <c r="K66" s="103" t="s">
+      <c r="J66" s="93"/>
+      <c r="K66" s="94" t="s">
         <v>326</v>
       </c>
-      <c r="L66" s="41"/>
-      <c r="M66" s="110"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="95"/>
       <c r="N66" s="87"/>
-      <c r="O66" s="111" t="s">
+      <c r="O66" s="96" t="s">
         <v>327</v>
       </c>
-      <c r="P66" s="111"/>
-      <c r="Q66" s="122"/>
+      <c r="P66" s="96"/>
+      <c r="Q66" s="97"/>
     </row>
     <row r="67" ht="17.55" spans="1:17">
-      <c r="A67" s="89"/>
-      <c r="B67" s="89"/>
-      <c r="C67" s="89"/>
-      <c r="D67" s="89"/>
-      <c r="E67" s="89"/>
-      <c r="F67" s="89"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="80"/>
-      <c r="I67" s="80"/>
-      <c r="J67" s="80"/>
-      <c r="K67" s="80"/>
-      <c r="L67" s="41"/>
-      <c r="M67" s="112" t="s">
+      <c r="A67" s="98"/>
+      <c r="B67" s="98"/>
+      <c r="C67" s="98"/>
+      <c r="D67" s="98"/>
+      <c r="E67" s="98"/>
+      <c r="F67" s="98"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="52"/>
+      <c r="J67" s="52"/>
+      <c r="K67" s="52"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="99" t="s">
         <v>328</v>
       </c>
-      <c r="N67" s="80"/>
-      <c r="O67" s="80"/>
-      <c r="P67" s="80"/>
-      <c r="Q67" s="80"/>
+      <c r="N67" s="52"/>
+      <c r="O67" s="52"/>
+      <c r="P67" s="52"/>
+      <c r="Q67" s="52"/>
     </row>
     <row r="68" spans="1:17">
-      <c r="A68" s="89"/>
-      <c r="B68" s="89"/>
-      <c r="C68" s="89"/>
-      <c r="D68" s="89"/>
-      <c r="E68" s="89"/>
-      <c r="F68" s="89"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="80"/>
-      <c r="J68" s="80"/>
-      <c r="K68" s="80"/>
-      <c r="L68" s="41"/>
-      <c r="M68" s="80"/>
-      <c r="N68" s="80"/>
-      <c r="O68" s="80"/>
-      <c r="P68" s="80"/>
-      <c r="Q68" s="80"/>
+      <c r="A68" s="98"/>
+      <c r="B68" s="98"/>
+      <c r="C68" s="98"/>
+      <c r="D68" s="98"/>
+      <c r="E68" s="98"/>
+      <c r="F68" s="98"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="52"/>
+      <c r="I68" s="52"/>
+      <c r="J68" s="52"/>
+      <c r="K68" s="52"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="52"/>
+      <c r="N68" s="52"/>
+      <c r="O68" s="52"/>
+      <c r="P68" s="52"/>
+      <c r="Q68" s="52"/>
     </row>
-    <row r="69" spans="7:17">
-      <c r="G69" s="19"/>
-      <c r="J69" s="80"/>
-      <c r="K69" s="80"/>
-      <c r="L69" s="41"/>
-      <c r="M69" s="80"/>
-      <c r="N69" s="80"/>
-      <c r="O69" s="80"/>
-      <c r="P69" s="80"/>
-      <c r="Q69" s="80"/>
+    <row r="69" spans="1:17">
+      <c r="G69" s="9"/>
+      <c r="J69" s="52"/>
+      <c r="K69" s="52"/>
+      <c r="L69" s="10"/>
+      <c r="M69" s="52"/>
+      <c r="N69" s="52"/>
+      <c r="O69" s="52"/>
+      <c r="P69" s="52"/>
+      <c r="Q69" s="52"/>
     </row>
-    <row r="70" spans="7:17">
-      <c r="G70" s="19"/>
-      <c r="J70" s="80"/>
-      <c r="K70" s="80"/>
-      <c r="L70" s="41"/>
-      <c r="M70" s="80"/>
-      <c r="N70" s="80"/>
-      <c r="O70" s="80"/>
-      <c r="P70" s="80"/>
-      <c r="Q70" s="80"/>
+    <row r="70" spans="1:17">
+      <c r="G70" s="9"/>
+      <c r="J70" s="52"/>
+      <c r="K70" s="52"/>
+      <c r="L70" s="10"/>
+      <c r="M70" s="52"/>
+      <c r="N70" s="52"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="52"/>
+      <c r="Q70" s="52"/>
     </row>
-    <row r="71" spans="7:17">
-      <c r="G71" s="19"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="80"/>
-      <c r="L71" s="41"/>
-      <c r="M71" s="80"/>
-      <c r="N71" s="80"/>
-      <c r="O71" s="80"/>
-      <c r="P71" s="80"/>
-      <c r="Q71" s="80"/>
+    <row r="71" spans="1:17">
+      <c r="G71" s="9"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="10"/>
+      <c r="M71" s="52"/>
+      <c r="N71" s="52"/>
+      <c r="O71" s="52"/>
+      <c r="P71" s="52"/>
+      <c r="Q71" s="52"/>
     </row>
-    <row r="72" spans="7:17">
-      <c r="G72" s="19"/>
-      <c r="J72" s="80"/>
-      <c r="K72" s="80"/>
-      <c r="L72" s="41"/>
-      <c r="M72" s="80"/>
-      <c r="N72" s="80"/>
-      <c r="O72" s="80"/>
-      <c r="P72" s="80"/>
-      <c r="Q72" s="80"/>
+    <row r="72" spans="1:17">
+      <c r="G72" s="9"/>
+      <c r="J72" s="52"/>
+      <c r="K72" s="52"/>
+      <c r="L72" s="10"/>
+      <c r="M72" s="52"/>
+      <c r="N72" s="52"/>
+      <c r="O72" s="52"/>
+      <c r="P72" s="52"/>
+      <c r="Q72" s="52"/>
     </row>
-    <row r="73" spans="7:17">
-      <c r="G73" s="19"/>
-      <c r="J73" s="80"/>
-      <c r="K73" s="80"/>
-      <c r="L73" s="41"/>
-      <c r="M73" s="80"/>
-      <c r="N73" s="80"/>
-      <c r="O73" s="80"/>
-      <c r="P73" s="80"/>
-      <c r="Q73" s="80"/>
+    <row r="73" spans="1:17">
+      <c r="G73" s="9"/>
+      <c r="J73" s="52"/>
+      <c r="K73" s="52"/>
+      <c r="L73" s="10"/>
+      <c r="M73" s="52"/>
+      <c r="N73" s="52"/>
+      <c r="O73" s="52"/>
+      <c r="P73" s="52"/>
+      <c r="Q73" s="52"/>
     </row>
-    <row r="74" spans="7:17">
-      <c r="G74" s="19"/>
-      <c r="J74" s="80"/>
-      <c r="K74" s="80"/>
-      <c r="L74" s="41"/>
-      <c r="M74" s="80"/>
-      <c r="N74" s="80"/>
-      <c r="O74" s="80"/>
-      <c r="P74" s="80"/>
-      <c r="Q74" s="80"/>
+    <row r="74" spans="1:17">
+      <c r="G74" s="9"/>
+      <c r="J74" s="52"/>
+      <c r="K74" s="52"/>
+      <c r="L74" s="10"/>
+      <c r="M74" s="52"/>
+      <c r="N74" s="52"/>
+      <c r="O74" s="52"/>
+      <c r="P74" s="52"/>
+      <c r="Q74" s="52"/>
     </row>
-    <row r="75" spans="7:17">
-      <c r="G75" s="19"/>
-      <c r="J75" s="80"/>
-      <c r="K75" s="80"/>
-      <c r="L75" s="41"/>
-      <c r="M75" s="80"/>
-      <c r="N75" s="80"/>
-      <c r="O75" s="80"/>
-      <c r="P75" s="80"/>
-      <c r="Q75" s="80"/>
+    <row r="75" spans="1:17">
+      <c r="G75" s="9"/>
+      <c r="J75" s="52"/>
+      <c r="K75" s="52"/>
+      <c r="L75" s="10"/>
+      <c r="M75" s="52"/>
+      <c r="N75" s="52"/>
+      <c r="O75" s="52"/>
+      <c r="P75" s="52"/>
+      <c r="Q75" s="52"/>
     </row>
-    <row r="76" spans="7:17">
-      <c r="G76" s="19"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="41"/>
-      <c r="M76" s="80"/>
-      <c r="N76" s="80"/>
-      <c r="O76" s="80"/>
-      <c r="P76" s="80"/>
-      <c r="Q76" s="80"/>
+    <row r="76" spans="1:17">
+      <c r="G76" s="9"/>
+      <c r="J76" s="52"/>
+      <c r="K76" s="52"/>
+      <c r="L76" s="10"/>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="52"/>
+      <c r="P76" s="52"/>
+      <c r="Q76" s="52"/>
     </row>
-    <row r="77" spans="7:17">
-      <c r="G77" s="19"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="80"/>
-      <c r="L77" s="41"/>
-      <c r="M77" s="80"/>
-      <c r="N77" s="80"/>
-      <c r="O77" s="80"/>
-      <c r="P77" s="80"/>
-      <c r="Q77" s="80"/>
+    <row r="77" spans="1:17">
+      <c r="G77" s="9"/>
+      <c r="J77" s="52"/>
+      <c r="K77" s="52"/>
+      <c r="L77" s="10"/>
+      <c r="M77" s="52"/>
+      <c r="N77" s="52"/>
+      <c r="O77" s="52"/>
+      <c r="P77" s="52"/>
+      <c r="Q77" s="52"/>
     </row>
-    <row r="78" spans="7:17">
-      <c r="G78" s="19"/>
-      <c r="J78" s="80"/>
-      <c r="K78" s="80"/>
-      <c r="L78" s="41"/>
-      <c r="M78" s="80"/>
-      <c r="N78" s="80"/>
-      <c r="O78" s="80"/>
-      <c r="P78" s="80"/>
-      <c r="Q78" s="80"/>
+    <row r="78" spans="1:17">
+      <c r="G78" s="9"/>
+      <c r="J78" s="52"/>
+      <c r="K78" s="52"/>
+      <c r="L78" s="10"/>
+      <c r="M78" s="52"/>
+      <c r="N78" s="52"/>
+      <c r="O78" s="52"/>
+      <c r="P78" s="52"/>
+      <c r="Q78" s="52"/>
     </row>
-    <row r="79" spans="7:17">
-      <c r="G79" s="19"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="80"/>
-      <c r="L79" s="41"/>
-      <c r="M79" s="80"/>
-      <c r="N79" s="80"/>
-      <c r="O79" s="80"/>
-      <c r="P79" s="80"/>
-      <c r="Q79" s="80"/>
+    <row r="79" spans="1:17">
+      <c r="G79" s="9"/>
+      <c r="J79" s="52"/>
+      <c r="K79" s="52"/>
+      <c r="L79" s="10"/>
+      <c r="M79" s="52"/>
+      <c r="N79" s="52"/>
+      <c r="O79" s="52"/>
+      <c r="P79" s="52"/>
+      <c r="Q79" s="52"/>
     </row>
-    <row r="80" spans="7:17">
-      <c r="G80" s="19"/>
-      <c r="J80" s="80"/>
-      <c r="K80" s="80"/>
-      <c r="L80" s="41"/>
-      <c r="M80" s="80"/>
-      <c r="N80" s="80"/>
-      <c r="O80" s="80"/>
-      <c r="P80" s="80"/>
-      <c r="Q80" s="80"/>
+    <row r="80" spans="1:17">
+      <c r="G80" s="9"/>
+      <c r="J80" s="52"/>
+      <c r="K80" s="52"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="52"/>
+      <c r="N80" s="52"/>
+      <c r="O80" s="52"/>
+      <c r="P80" s="52"/>
+      <c r="Q80" s="52"/>
     </row>
-    <row r="81" spans="7:17">
-      <c r="G81" s="19"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="80"/>
-      <c r="L81" s="41"/>
-      <c r="M81" s="80"/>
-      <c r="N81" s="80"/>
-      <c r="O81" s="80"/>
-      <c r="P81" s="80"/>
-      <c r="Q81" s="80"/>
+    <row r="81" spans="1:17">
+      <c r="G81" s="9"/>
+      <c r="J81" s="52"/>
+      <c r="K81" s="52"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="52"/>
+      <c r="N81" s="52"/>
+      <c r="O81" s="52"/>
+      <c r="P81" s="52"/>
+      <c r="Q81" s="52"/>
     </row>
-    <row r="82" spans="7:17">
-      <c r="G82" s="19"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="41"/>
-      <c r="M82" s="80"/>
-      <c r="N82" s="80"/>
-      <c r="O82" s="80"/>
-      <c r="P82" s="80"/>
-      <c r="Q82" s="80"/>
+    <row r="82" spans="1:17">
+      <c r="G82" s="9"/>
+      <c r="J82" s="52"/>
+      <c r="K82" s="52"/>
+      <c r="L82" s="10"/>
+      <c r="M82" s="52"/>
+      <c r="N82" s="52"/>
+      <c r="O82" s="52"/>
+      <c r="P82" s="52"/>
+      <c r="Q82" s="52"/>
     </row>
-    <row r="83" spans="7:17">
-      <c r="G83" s="19"/>
-      <c r="J83" s="80"/>
-      <c r="K83" s="80"/>
-      <c r="L83" s="41"/>
-      <c r="M83" s="80"/>
-      <c r="N83" s="80"/>
-      <c r="O83" s="80"/>
-      <c r="P83" s="80"/>
-      <c r="Q83" s="80"/>
+    <row r="83" spans="1:17">
+      <c r="G83" s="9"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52"/>
+      <c r="O83" s="52"/>
+      <c r="P83" s="52"/>
+      <c r="Q83" s="52"/>
     </row>
-    <row r="84" spans="7:17">
-      <c r="G84" s="19"/>
-      <c r="J84" s="80"/>
-      <c r="K84" s="80"/>
-      <c r="L84" s="41"/>
-      <c r="M84" s="80"/>
-      <c r="N84" s="80"/>
-      <c r="O84" s="80"/>
-      <c r="P84" s="80"/>
-      <c r="Q84" s="80"/>
+    <row r="84" spans="1:17">
+      <c r="G84" s="9"/>
+      <c r="J84" s="52"/>
+      <c r="K84" s="52"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="52"/>
+      <c r="N84" s="52"/>
+      <c r="O84" s="52"/>
+      <c r="P84" s="52"/>
+      <c r="Q84" s="52"/>
     </row>
-    <row r="85" spans="7:17">
-      <c r="G85" s="19"/>
-      <c r="J85" s="80"/>
-      <c r="K85" s="80"/>
-      <c r="L85" s="41"/>
-      <c r="M85" s="80"/>
-      <c r="N85" s="80"/>
-      <c r="O85" s="80"/>
-      <c r="P85" s="80"/>
-      <c r="Q85" s="80"/>
+    <row r="85" spans="1:17">
+      <c r="G85" s="9"/>
+      <c r="J85" s="52"/>
+      <c r="K85" s="52"/>
+      <c r="L85" s="10"/>
+      <c r="M85" s="52"/>
+      <c r="N85" s="52"/>
+      <c r="O85" s="52"/>
+      <c r="P85" s="52"/>
+      <c r="Q85" s="52"/>
     </row>
-    <row r="86" spans="7:17">
-      <c r="G86" s="19"/>
-      <c r="J86" s="80"/>
-      <c r="K86" s="80"/>
-      <c r="L86" s="41"/>
-      <c r="M86" s="80"/>
-      <c r="N86" s="80"/>
-      <c r="O86" s="80"/>
-      <c r="P86" s="80"/>
-      <c r="Q86" s="80"/>
+    <row r="86" spans="1:17">
+      <c r="G86" s="9"/>
+      <c r="J86" s="52"/>
+      <c r="K86" s="52"/>
+      <c r="L86" s="10"/>
+      <c r="M86" s="52"/>
+      <c r="N86" s="52"/>
+      <c r="O86" s="52"/>
+      <c r="P86" s="52"/>
+      <c r="Q86" s="52"/>
     </row>
-    <row r="87" spans="7:17">
-      <c r="G87" s="19"/>
-      <c r="J87" s="80"/>
-      <c r="K87" s="80"/>
-      <c r="L87" s="41"/>
-      <c r="M87" s="80"/>
-      <c r="N87" s="80"/>
-      <c r="O87" s="80"/>
-      <c r="P87" s="80"/>
-      <c r="Q87" s="80"/>
+    <row r="87" spans="1:17">
+      <c r="G87" s="9"/>
+      <c r="J87" s="52"/>
+      <c r="K87" s="52"/>
+      <c r="L87" s="10"/>
+      <c r="M87" s="52"/>
+      <c r="N87" s="52"/>
+      <c r="O87" s="52"/>
+      <c r="P87" s="52"/>
+      <c r="Q87" s="52"/>
     </row>
-    <row r="88" spans="7:17">
-      <c r="G88" s="19"/>
-      <c r="J88" s="80"/>
-      <c r="K88" s="80"/>
-      <c r="L88" s="41"/>
-      <c r="M88" s="80"/>
-      <c r="N88" s="80"/>
-      <c r="O88" s="80"/>
-      <c r="P88" s="80"/>
-      <c r="Q88" s="80"/>
+    <row r="88" spans="1:17">
+      <c r="G88" s="9"/>
+      <c r="J88" s="52"/>
+      <c r="K88" s="52"/>
+      <c r="L88" s="10"/>
+      <c r="M88" s="52"/>
+      <c r="N88" s="52"/>
+      <c r="O88" s="52"/>
+      <c r="P88" s="52"/>
+      <c r="Q88" s="52"/>
     </row>
-    <row r="89" spans="7:17">
-      <c r="G89" s="19"/>
-      <c r="J89" s="80"/>
-      <c r="K89" s="80"/>
-      <c r="L89" s="41"/>
-      <c r="M89" s="80"/>
-      <c r="N89" s="80"/>
-      <c r="O89" s="80"/>
-      <c r="P89" s="80"/>
-      <c r="Q89" s="80"/>
+    <row r="89" spans="1:17">
+      <c r="G89" s="9"/>
+      <c r="J89" s="52"/>
+      <c r="K89" s="52"/>
+      <c r="L89" s="10"/>
+      <c r="M89" s="52"/>
+      <c r="N89" s="52"/>
+      <c r="O89" s="52"/>
+      <c r="P89" s="52"/>
+      <c r="Q89" s="52"/>
     </row>
-    <row r="90" spans="7:17">
-      <c r="G90" s="19"/>
-      <c r="J90" s="80"/>
-      <c r="K90" s="80"/>
-      <c r="L90" s="41"/>
-      <c r="M90" s="80"/>
-      <c r="N90" s="80"/>
-      <c r="O90" s="80"/>
-      <c r="P90" s="80"/>
-      <c r="Q90" s="80"/>
+    <row r="90" spans="1:17">
+      <c r="G90" s="9"/>
+      <c r="J90" s="52"/>
+      <c r="K90" s="52"/>
+      <c r="L90" s="10"/>
+      <c r="M90" s="52"/>
+      <c r="N90" s="52"/>
+      <c r="O90" s="52"/>
+      <c r="P90" s="52"/>
+      <c r="Q90" s="52"/>
     </row>
-    <row r="91" spans="7:17">
-      <c r="G91" s="19"/>
-      <c r="J91" s="80"/>
-      <c r="K91" s="80"/>
-      <c r="L91" s="41"/>
-      <c r="M91" s="80"/>
-      <c r="N91" s="80"/>
-      <c r="O91" s="80"/>
-      <c r="P91" s="80"/>
-      <c r="Q91" s="80"/>
+    <row r="91" spans="1:17">
+      <c r="G91" s="9"/>
+      <c r="J91" s="52"/>
+      <c r="K91" s="52"/>
+      <c r="L91" s="10"/>
+      <c r="M91" s="52"/>
+      <c r="N91" s="52"/>
+      <c r="O91" s="52"/>
+      <c r="P91" s="52"/>
+      <c r="Q91" s="52"/>
     </row>
-    <row r="92" spans="7:17">
-      <c r="G92" s="19"/>
-      <c r="J92" s="80"/>
-      <c r="K92" s="80"/>
-      <c r="L92" s="41"/>
-      <c r="M92" s="80"/>
-      <c r="N92" s="80"/>
-      <c r="O92" s="80"/>
-      <c r="P92" s="80"/>
-      <c r="Q92" s="80"/>
+    <row r="92" spans="1:17">
+      <c r="G92" s="9"/>
+      <c r="J92" s="52"/>
+      <c r="K92" s="52"/>
+      <c r="L92" s="10"/>
+      <c r="M92" s="52"/>
+      <c r="N92" s="52"/>
+      <c r="O92" s="52"/>
+      <c r="P92" s="52"/>
+      <c r="Q92" s="52"/>
     </row>
     <row r="93" spans="1:17">
-      <c r="A93" s="89"/>
-      <c r="B93" s="89"/>
-      <c r="C93" s="89"/>
-      <c r="D93" s="89"/>
-      <c r="E93" s="89"/>
-      <c r="F93" s="89"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="80"/>
-      <c r="J93" s="80"/>
-      <c r="K93" s="80"/>
-      <c r="L93" s="41"/>
-      <c r="M93" s="80"/>
-      <c r="N93" s="80"/>
-      <c r="O93" s="80"/>
-      <c r="P93" s="80"/>
-      <c r="Q93" s="80"/>
+      <c r="A93" s="98"/>
+      <c r="B93" s="98"/>
+      <c r="C93" s="98"/>
+      <c r="D93" s="98"/>
+      <c r="E93" s="98"/>
+      <c r="F93" s="98"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="52"/>
+      <c r="I93" s="52"/>
+      <c r="J93" s="52"/>
+      <c r="K93" s="52"/>
+      <c r="L93" s="10"/>
+      <c r="M93" s="52"/>
+      <c r="N93" s="52"/>
+      <c r="O93" s="52"/>
+      <c r="P93" s="52"/>
+      <c r="Q93" s="52"/>
     </row>
     <row r="94" ht="17.55" spans="1:17">
-      <c r="A94" s="89"/>
-      <c r="B94" s="89"/>
-      <c r="C94" s="89"/>
-      <c r="D94" s="89"/>
-      <c r="E94" s="89"/>
-      <c r="F94" s="89"/>
-      <c r="G94" s="19"/>
-      <c r="H94" s="80"/>
-      <c r="I94" s="80"/>
-      <c r="J94" s="80"/>
-      <c r="K94" s="80"/>
-      <c r="L94" s="41"/>
-      <c r="M94" s="80"/>
-      <c r="N94" s="80"/>
-      <c r="O94" s="80"/>
-      <c r="P94" s="80"/>
-      <c r="Q94" s="80"/>
+      <c r="A94" s="98"/>
+      <c r="B94" s="98"/>
+      <c r="C94" s="98"/>
+      <c r="D94" s="98"/>
+      <c r="E94" s="98"/>
+      <c r="F94" s="98"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="52"/>
+      <c r="I94" s="52"/>
+      <c r="J94" s="52"/>
+      <c r="K94" s="52"/>
+      <c r="L94" s="10"/>
+      <c r="M94" s="52"/>
+      <c r="N94" s="52"/>
+      <c r="O94" s="52"/>
+      <c r="P94" s="52"/>
+      <c r="Q94" s="52"/>
     </row>
     <row r="95" ht="22.5" spans="1:17">
       <c r="A95" s="5" t="s">
@@ -12627,1233 +12639,1233 @@
       <c r="C95" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E95" s="18"/>
+      <c r="E95" s="8"/>
       <c r="F95" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G95" s="19"/>
-      <c r="H95" s="73" t="s">
+      <c r="G95" s="9"/>
+      <c r="H95" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I95" s="77"/>
-      <c r="J95" s="77"/>
-      <c r="K95" s="83"/>
-      <c r="L95" s="41"/>
-      <c r="M95" s="73" t="s">
+      <c r="I95" s="47"/>
+      <c r="J95" s="47"/>
+      <c r="K95" s="48"/>
+      <c r="L95" s="10"/>
+      <c r="M95" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="N95" s="77"/>
-      <c r="O95" s="77"/>
-      <c r="P95" s="77"/>
-      <c r="Q95" s="83"/>
+      <c r="N95" s="47"/>
+      <c r="O95" s="47"/>
+      <c r="P95" s="47"/>
+      <c r="Q95" s="48"/>
     </row>
     <row r="96" ht="18.3" spans="1:17">
       <c r="A96" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="D96" s="27" t="s">
+      <c r="D96" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="E96" s="95"/>
-      <c r="F96" s="43" t="s">
+      <c r="E96" s="100"/>
+      <c r="F96" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G96" s="19"/>
-      <c r="H96" s="96" t="s">
+      <c r="G96" s="9"/>
+      <c r="H96" s="101" t="s">
         <v>336</v>
       </c>
-      <c r="I96" s="104" t="s">
+      <c r="I96" s="102" t="s">
         <v>337</v>
       </c>
-      <c r="J96" s="104" t="s">
+      <c r="J96" s="102" t="s">
         <v>338</v>
       </c>
-      <c r="K96" s="105" t="s">
+      <c r="K96" s="103" t="s">
         <v>339</v>
       </c>
-      <c r="L96" s="41"/>
-      <c r="M96" s="113" t="s">
+      <c r="L96" s="10"/>
+      <c r="M96" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="N96" s="114" t="s">
+      <c r="N96" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="O96" s="115"/>
-      <c r="P96" s="116" t="s">
+      <c r="O96" s="106"/>
+      <c r="P96" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="123"/>
+      <c r="Q96" s="108"/>
     </row>
     <row r="97" ht="18.3" spans="1:17">
-      <c r="A97" s="90"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="27" t="s">
+      <c r="A97" s="109"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="E97" s="95"/>
-      <c r="F97" s="97" t="s">
+      <c r="E97" s="100"/>
+      <c r="F97" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G97" s="19"/>
-      <c r="H97" s="98" t="s">
+      <c r="G97" s="9"/>
+      <c r="H97" s="111" t="s">
         <v>342</v>
       </c>
-      <c r="I97" s="106" t="s">
+      <c r="I97" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J97" s="106" t="s">
+      <c r="J97" s="112" t="s">
         <v>344</v>
       </c>
-      <c r="K97" s="82" t="s">
+      <c r="K97" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L97" s="41"/>
+      <c r="L97" s="10"/>
       <c r="M97" s="129" t="s">
         <v>345</v>
       </c>
-      <c r="N97" s="118" t="s">
+      <c r="N97" s="114" t="s">
         <v>346</v>
       </c>
-      <c r="O97" s="119"/>
-      <c r="P97" s="80" t="s">
+      <c r="O97" s="115"/>
+      <c r="P97" s="52" t="s">
         <v>347</v>
       </c>
-      <c r="Q97" s="84"/>
+      <c r="Q97" s="51"/>
     </row>
     <row r="98" ht="18.3" spans="1:17">
-      <c r="A98" s="90"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="12" t="s">
+      <c r="A98" s="109"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="D98" s="27" t="s">
+      <c r="D98" s="37" t="s">
         <v>349</v>
       </c>
-      <c r="E98" s="95"/>
-      <c r="F98" s="97" t="s">
+      <c r="E98" s="100"/>
+      <c r="F98" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G98" s="19"/>
-      <c r="H98" s="98"/>
-      <c r="I98" s="106" t="s">
+      <c r="G98" s="9"/>
+      <c r="H98" s="111"/>
+      <c r="I98" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J98" s="106" t="s">
+      <c r="J98" s="112" t="s">
         <v>351</v>
       </c>
-      <c r="K98" s="82" t="s">
+      <c r="K98" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L98" s="41"/>
+      <c r="L98" s="10"/>
       <c r="M98" s="129" t="s">
         <v>352</v>
       </c>
-      <c r="N98" s="118" t="s">
+      <c r="N98" s="114" t="s">
         <v>353</v>
       </c>
-      <c r="O98" s="119"/>
-      <c r="P98" s="80" t="s">
+      <c r="O98" s="115"/>
+      <c r="P98" s="52" t="s">
         <v>354</v>
       </c>
-      <c r="Q98" s="84"/>
+      <c r="Q98" s="51"/>
     </row>
     <row r="99" ht="18.3" spans="1:17">
-      <c r="A99" s="90"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="27" t="s">
+      <c r="A99" s="109"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="37" t="s">
         <v>355</v>
       </c>
-      <c r="E99" s="95"/>
-      <c r="F99" s="97" t="s">
+      <c r="E99" s="100"/>
+      <c r="F99" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G99" s="19"/>
-      <c r="H99" s="98"/>
-      <c r="I99" s="106" t="s">
+      <c r="G99" s="9"/>
+      <c r="H99" s="111"/>
+      <c r="I99" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J99" s="106" t="s">
+      <c r="J99" s="112" t="s">
         <v>357</v>
       </c>
-      <c r="K99" s="82" t="s">
+      <c r="K99" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L99" s="41"/>
+      <c r="L99" s="10"/>
       <c r="M99" s="129" t="s">
         <v>358</v>
       </c>
-      <c r="N99" s="118" t="s">
+      <c r="N99" s="114" t="s">
         <v>359</v>
       </c>
-      <c r="O99" s="119"/>
-      <c r="P99" s="80" t="s">
+      <c r="O99" s="115"/>
+      <c r="P99" s="52" t="s">
         <v>360</v>
       </c>
-      <c r="Q99" s="84"/>
+      <c r="Q99" s="51"/>
     </row>
     <row r="100" ht="18.3" spans="1:17">
-      <c r="A100" s="90"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="12" t="s">
+      <c r="A100" s="109"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="D100" s="27" t="s">
+      <c r="D100" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="E100" s="95"/>
-      <c r="F100" s="97" t="s">
+      <c r="E100" s="100"/>
+      <c r="F100" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G100" s="19"/>
-      <c r="H100" s="98"/>
-      <c r="I100" s="106" t="s">
+      <c r="G100" s="9"/>
+      <c r="H100" s="111"/>
+      <c r="I100" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J100" s="106" t="s">
+      <c r="J100" s="112" t="s">
         <v>364</v>
       </c>
-      <c r="K100" s="82" t="s">
+      <c r="K100" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L100" s="41"/>
+      <c r="L100" s="10"/>
       <c r="M100" s="129" t="s">
         <v>365</v>
       </c>
-      <c r="N100" s="118" t="s">
+      <c r="N100" s="114" t="s">
         <v>366</v>
       </c>
-      <c r="O100" s="119"/>
-      <c r="P100" s="80" t="s">
+      <c r="O100" s="115"/>
+      <c r="P100" s="52" t="s">
         <v>367</v>
       </c>
-      <c r="Q100" s="84"/>
+      <c r="Q100" s="51"/>
     </row>
     <row r="101" ht="18.3" spans="1:17">
-      <c r="A101" s="90"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="27" t="s">
+      <c r="A101" s="109"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="37" t="s">
         <v>368</v>
       </c>
-      <c r="E101" s="95"/>
-      <c r="F101" s="97" t="s">
+      <c r="E101" s="100"/>
+      <c r="F101" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G101" s="19"/>
-      <c r="H101" s="98"/>
-      <c r="I101" s="106" t="s">
+      <c r="G101" s="9"/>
+      <c r="H101" s="111"/>
+      <c r="I101" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J101" s="106" t="s">
+      <c r="J101" s="112" t="s">
         <v>370</v>
       </c>
-      <c r="K101" s="82" t="s">
+      <c r="K101" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L101" s="41"/>
+      <c r="L101" s="10"/>
       <c r="M101" s="129" t="s">
         <v>371</v>
       </c>
-      <c r="N101" s="118" t="s">
+      <c r="N101" s="114" t="s">
         <v>372</v>
       </c>
-      <c r="O101" s="119"/>
-      <c r="P101" s="80" t="s">
+      <c r="O101" s="115"/>
+      <c r="P101" s="52" t="s">
         <v>373</v>
       </c>
-      <c r="Q101" s="84"/>
+      <c r="Q101" s="51"/>
     </row>
     <row r="102" ht="18.3" spans="1:17">
-      <c r="A102" s="90"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="27" t="s">
+      <c r="A102" s="109"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="37" t="s">
         <v>374</v>
       </c>
-      <c r="E102" s="95"/>
-      <c r="F102" s="97" t="s">
+      <c r="E102" s="100"/>
+      <c r="F102" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="G102" s="19"/>
-      <c r="H102" s="98"/>
-      <c r="I102" s="106" t="s">
+      <c r="G102" s="9"/>
+      <c r="H102" s="111"/>
+      <c r="I102" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J102" s="106" t="s">
+      <c r="J102" s="112" t="s">
         <v>376</v>
       </c>
-      <c r="K102" s="82" t="s">
+      <c r="K102" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L102" s="41"/>
+      <c r="L102" s="10"/>
       <c r="M102" s="129" t="s">
         <v>377</v>
       </c>
-      <c r="N102" s="118" t="s">
+      <c r="N102" s="114" t="s">
         <v>378</v>
       </c>
-      <c r="O102" s="119"/>
-      <c r="P102" s="80" t="s">
+      <c r="O102" s="115"/>
+      <c r="P102" s="52" t="s">
         <v>379</v>
       </c>
-      <c r="Q102" s="84"/>
+      <c r="Q102" s="51"/>
     </row>
     <row r="103" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A103" s="90"/>
-      <c r="B103" s="11" t="s">
+      <c r="A103" s="109"/>
+      <c r="B103" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="D103" s="27" t="s">
+      <c r="D103" s="37" t="s">
         <v>382</v>
       </c>
-      <c r="E103" s="95"/>
-      <c r="F103" s="43" t="s">
+      <c r="E103" s="100"/>
+      <c r="F103" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G103" s="19"/>
-      <c r="H103" s="98"/>
-      <c r="I103" s="106" t="s">
+      <c r="G103" s="9"/>
+      <c r="H103" s="111"/>
+      <c r="I103" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J103" s="106" t="s">
+      <c r="J103" s="112" t="s">
         <v>383</v>
       </c>
-      <c r="K103" s="82" t="s">
+      <c r="K103" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L103" s="41"/>
+      <c r="L103" s="10"/>
       <c r="M103" s="129" t="s">
         <v>384</v>
       </c>
-      <c r="N103" s="118" t="s">
+      <c r="N103" s="114" t="s">
         <v>385</v>
       </c>
-      <c r="O103" s="119"/>
-      <c r="P103" s="80" t="s">
+      <c r="O103" s="115"/>
+      <c r="P103" s="52" t="s">
         <v>386</v>
       </c>
-      <c r="Q103" s="84"/>
+      <c r="Q103" s="51"/>
     </row>
     <row r="104" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A104" s="90"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="27" t="s">
+      <c r="A104" s="109"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="37" t="s">
         <v>387</v>
       </c>
-      <c r="E104" s="95"/>
-      <c r="F104" s="97" t="s">
+      <c r="E104" s="100"/>
+      <c r="F104" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G104" s="19"/>
-      <c r="H104" s="98"/>
-      <c r="I104" s="106" t="s">
+      <c r="G104" s="9"/>
+      <c r="H104" s="111"/>
+      <c r="I104" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J104" s="106" t="s">
+      <c r="J104" s="112" t="s">
         <v>388</v>
       </c>
-      <c r="K104" s="82" t="s">
+      <c r="K104" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L104" s="41"/>
+      <c r="L104" s="10"/>
       <c r="M104" s="129" t="s">
         <v>389</v>
       </c>
-      <c r="N104" s="118" t="s">
+      <c r="N104" s="114" t="s">
         <v>390</v>
       </c>
-      <c r="O104" s="119"/>
-      <c r="P104" s="80" t="s">
+      <c r="O104" s="115"/>
+      <c r="P104" s="52" t="s">
         <v>391</v>
       </c>
-      <c r="Q104" s="84"/>
+      <c r="Q104" s="51"/>
     </row>
     <row r="105" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A105" s="90"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="15" t="s">
+      <c r="A105" s="109"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="45" t="s">
         <v>392</v>
       </c>
-      <c r="D105" s="91" t="s">
+      <c r="D105" s="116" t="s">
         <v>393</v>
       </c>
-      <c r="E105" s="95"/>
-      <c r="F105" s="97" t="s">
+      <c r="E105" s="100"/>
+      <c r="F105" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G105" s="19"/>
-      <c r="H105" s="98"/>
-      <c r="I105" s="106" t="s">
+      <c r="G105" s="9"/>
+      <c r="H105" s="111"/>
+      <c r="I105" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J105" s="106" t="s">
+      <c r="J105" s="112" t="s">
         <v>394</v>
       </c>
-      <c r="K105" s="82" t="s">
+      <c r="K105" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L105" s="41"/>
+      <c r="L105" s="10"/>
       <c r="M105" s="129" t="s">
         <v>395</v>
       </c>
-      <c r="N105" s="118" t="s">
+      <c r="N105" s="114" t="s">
         <v>396</v>
       </c>
-      <c r="O105" s="119"/>
-      <c r="P105" s="80" t="s">
+      <c r="O105" s="115"/>
+      <c r="P105" s="52" t="s">
         <v>397</v>
       </c>
-      <c r="Q105" s="84"/>
+      <c r="Q105" s="51"/>
     </row>
     <row r="106" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A106" s="90"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="91" t="s">
+      <c r="A106" s="109"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="116" t="s">
         <v>398</v>
       </c>
-      <c r="E106" s="95"/>
-      <c r="F106" s="97" t="s">
+      <c r="E106" s="100"/>
+      <c r="F106" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G106" s="19"/>
-      <c r="H106" s="98"/>
-      <c r="I106" s="106" t="s">
+      <c r="G106" s="9"/>
+      <c r="H106" s="111"/>
+      <c r="I106" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J106" s="106" t="s">
+      <c r="J106" s="112" t="s">
         <v>399</v>
       </c>
-      <c r="K106" s="82" t="s">
+      <c r="K106" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="L106" s="41"/>
+      <c r="L106" s="10"/>
       <c r="M106" s="129" t="s">
         <v>400</v>
       </c>
-      <c r="N106" s="118" t="s">
+      <c r="N106" s="114" t="s">
         <v>401</v>
       </c>
-      <c r="O106" s="119"/>
-      <c r="P106" s="80" t="s">
+      <c r="O106" s="115"/>
+      <c r="P106" s="52" t="s">
         <v>402</v>
       </c>
-      <c r="Q106" s="84"/>
+      <c r="Q106" s="51"/>
     </row>
     <row r="107" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A107" s="90"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="15" t="s">
+      <c r="A107" s="109"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="45" t="s">
         <v>403</v>
       </c>
-      <c r="D107" s="91" t="s">
+      <c r="D107" s="116" t="s">
         <v>404</v>
       </c>
-      <c r="E107" s="95"/>
-      <c r="F107" s="97" t="s">
+      <c r="E107" s="100"/>
+      <c r="F107" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G107" s="19"/>
-      <c r="H107" s="98"/>
-      <c r="I107" s="106" t="s">
+      <c r="G107" s="9"/>
+      <c r="H107" s="111"/>
+      <c r="I107" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J107" s="106" t="s">
+      <c r="J107" s="112" t="s">
         <v>406</v>
       </c>
-      <c r="K107" s="82" t="s">
+      <c r="K107" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L107" s="41"/>
+      <c r="L107" s="10"/>
       <c r="M107" s="129" t="s">
         <v>407</v>
       </c>
-      <c r="N107" s="118" t="s">
+      <c r="N107" s="114" t="s">
         <v>408</v>
       </c>
-      <c r="O107" s="119"/>
-      <c r="P107" s="80" t="s">
+      <c r="O107" s="115"/>
+      <c r="P107" s="52" t="s">
         <v>409</v>
       </c>
-      <c r="Q107" s="84"/>
+      <c r="Q107" s="51"/>
     </row>
     <row r="108" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A108" s="90"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="15"/>
-      <c r="D108" s="91" t="s">
+      <c r="A108" s="109"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="45"/>
+      <c r="D108" s="116" t="s">
         <v>410</v>
       </c>
-      <c r="E108" s="95"/>
-      <c r="F108" s="97" t="s">
+      <c r="E108" s="100"/>
+      <c r="F108" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G108" s="19"/>
-      <c r="H108" s="98"/>
-      <c r="I108" s="106" t="s">
+      <c r="G108" s="9"/>
+      <c r="H108" s="111"/>
+      <c r="I108" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J108" s="106" t="s">
+      <c r="J108" s="112" t="s">
         <v>411</v>
       </c>
-      <c r="K108" s="82" t="s">
+      <c r="K108" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L108" s="41"/>
+      <c r="L108" s="10"/>
       <c r="M108" s="130" t="s">
         <v>412</v>
       </c>
-      <c r="N108" s="120" t="s">
+      <c r="N108" s="117" t="s">
         <v>413</v>
       </c>
-      <c r="O108" s="121"/>
-      <c r="P108" s="111" t="s">
+      <c r="O108" s="118"/>
+      <c r="P108" s="96" t="s">
         <v>414</v>
       </c>
-      <c r="Q108" s="122"/>
+      <c r="Q108" s="97"/>
     </row>
     <row r="109" customFormat="1" ht="18.3" spans="1:17">
-      <c r="A109" s="90"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="15"/>
-      <c r="D109" s="91" t="s">
+      <c r="A109" s="109"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="45"/>
+      <c r="D109" s="116" t="s">
         <v>415</v>
       </c>
-      <c r="E109" s="95"/>
-      <c r="F109" s="97" t="s">
+      <c r="E109" s="100"/>
+      <c r="F109" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="G109" s="19"/>
-      <c r="H109" s="98"/>
-      <c r="I109" s="106" t="s">
+      <c r="G109" s="9"/>
+      <c r="H109" s="111"/>
+      <c r="I109" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J109" s="106" t="s">
+      <c r="J109" s="112" t="s">
         <v>416</v>
       </c>
-      <c r="K109" s="82" t="s">
+      <c r="K109" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L109" s="41"/>
-      <c r="M109" s="80"/>
-      <c r="N109" s="80"/>
-      <c r="O109" s="80"/>
-      <c r="P109" s="80"/>
-      <c r="Q109" s="80"/>
+      <c r="L109" s="10"/>
+      <c r="M109" s="52"/>
+      <c r="N109" s="52"/>
+      <c r="O109" s="52"/>
+      <c r="P109" s="52"/>
+      <c r="Q109" s="52"/>
     </row>
-    <row r="110" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A110" s="90"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="15" t="s">
+    <row r="110" customFormat="1" ht="18.3" spans="1:17">
+      <c r="A110" s="109"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="45" t="s">
         <v>417</v>
       </c>
-      <c r="D110" s="91" t="s">
+      <c r="D110" s="116" t="s">
         <v>418</v>
       </c>
-      <c r="E110" s="95"/>
-      <c r="F110" s="43" t="s">
+      <c r="E110" s="100"/>
+      <c r="F110" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G110" s="19"/>
-      <c r="H110" s="98"/>
-      <c r="I110" s="106" t="s">
+      <c r="G110" s="9"/>
+      <c r="H110" s="111"/>
+      <c r="I110" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J110" s="106" t="s">
+      <c r="J110" s="112" t="s">
         <v>419</v>
       </c>
-      <c r="K110" s="82" t="s">
+      <c r="K110" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L110" s="41"/>
+      <c r="L110" s="10"/>
     </row>
-    <row r="111" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A111" s="90"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="91" t="s">
+    <row r="111" customFormat="1" ht="18.3" spans="1:17">
+      <c r="A111" s="109"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="116" t="s">
         <v>420</v>
       </c>
-      <c r="E111" s="95"/>
-      <c r="F111" s="97" t="s">
+      <c r="E111" s="100"/>
+      <c r="F111" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G111" s="19"/>
-      <c r="H111" s="98"/>
-      <c r="I111" s="106" t="s">
+      <c r="G111" s="9"/>
+      <c r="H111" s="111"/>
+      <c r="I111" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J111" s="106" t="s">
+      <c r="J111" s="112" t="s">
         <v>421</v>
       </c>
-      <c r="K111" s="82" t="s">
+      <c r="K111" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L111" s="41"/>
+      <c r="L111" s="10"/>
     </row>
-    <row r="112" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A112" s="90"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="15" t="s">
+    <row r="112" customFormat="1" ht="18.3" spans="1:17">
+      <c r="A112" s="109"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="D112" s="91" t="s">
+      <c r="D112" s="116" t="s">
         <v>423</v>
       </c>
-      <c r="E112" s="95"/>
-      <c r="F112" s="97" t="s">
+      <c r="E112" s="100"/>
+      <c r="F112" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G112" s="19"/>
-      <c r="H112" s="98"/>
-      <c r="I112" s="106" t="s">
+      <c r="G112" s="9"/>
+      <c r="H112" s="111"/>
+      <c r="I112" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J112" s="106" t="s">
+      <c r="J112" s="112" t="s">
         <v>424</v>
       </c>
-      <c r="K112" s="82" t="s">
+      <c r="K112" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="L112" s="41"/>
+      <c r="L112" s="10"/>
     </row>
     <row r="113" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A113" s="90"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="91" t="s">
+      <c r="A113" s="109"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="116" t="s">
         <v>425</v>
       </c>
-      <c r="E113" s="95"/>
-      <c r="F113" s="97" t="s">
+      <c r="E113" s="100"/>
+      <c r="F113" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G113" s="19"/>
-      <c r="H113" s="98"/>
-      <c r="I113" s="106" t="s">
+      <c r="G113" s="9"/>
+      <c r="H113" s="111"/>
+      <c r="I113" s="112" t="s">
         <v>426</v>
       </c>
-      <c r="J113" s="106" t="s">
+      <c r="J113" s="112" t="s">
         <v>427</v>
       </c>
-      <c r="K113" s="82" t="s">
+      <c r="K113" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="L113" s="41"/>
+      <c r="L113" s="10"/>
     </row>
     <row r="114" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A114" s="90"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="15" t="s">
+      <c r="A114" s="109"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="45" t="s">
         <v>428</v>
       </c>
-      <c r="D114" s="91" t="s">
+      <c r="D114" s="116" t="s">
         <v>429</v>
       </c>
-      <c r="E114" s="95"/>
-      <c r="F114" s="97" t="s">
+      <c r="E114" s="100"/>
+      <c r="F114" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G114" s="19"/>
-      <c r="H114" s="98"/>
-      <c r="I114" s="106" t="s">
+      <c r="G114" s="9"/>
+      <c r="H114" s="111"/>
+      <c r="I114" s="112" t="s">
         <v>426</v>
       </c>
-      <c r="J114" s="106" t="s">
+      <c r="J114" s="112" t="s">
         <v>430</v>
       </c>
-      <c r="K114" s="82" t="s">
+      <c r="K114" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="L114" s="41"/>
+      <c r="L114" s="10"/>
     </row>
     <row r="115" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A115" s="90"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="15"/>
-      <c r="D115" s="91" t="s">
+      <c r="A115" s="109"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="45"/>
+      <c r="D115" s="116" t="s">
         <v>431</v>
       </c>
-      <c r="E115" s="95"/>
-      <c r="F115" s="97" t="s">
+      <c r="E115" s="100"/>
+      <c r="F115" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G115" s="19"/>
-      <c r="H115" s="99" t="s">
+      <c r="G115" s="9"/>
+      <c r="H115" s="119" t="s">
         <v>432</v>
       </c>
-      <c r="I115" s="106" t="s">
+      <c r="I115" s="112" t="s">
         <v>433</v>
       </c>
-      <c r="J115" s="106" t="s">
+      <c r="J115" s="112" t="s">
         <v>434</v>
       </c>
-      <c r="K115" s="82" t="s">
+      <c r="K115" s="24" t="s">
         <v>435</v>
       </c>
-      <c r="L115" s="41"/>
+      <c r="L115" s="10"/>
     </row>
     <row r="116" customFormat="1" ht="18.3" spans="1:12">
-      <c r="A116" s="90"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="15"/>
-      <c r="D116" s="91" t="s">
+      <c r="A116" s="109"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="45"/>
+      <c r="D116" s="116" t="s">
         <v>436</v>
       </c>
-      <c r="E116" s="95"/>
-      <c r="F116" s="97" t="s">
+      <c r="E116" s="100"/>
+      <c r="F116" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="G116" s="19"/>
-      <c r="H116" s="100" t="s">
+      <c r="G116" s="9"/>
+      <c r="H116" s="120" t="s">
         <v>437</v>
       </c>
-      <c r="I116" s="106" t="s">
+      <c r="I116" s="112" t="s">
         <v>438</v>
       </c>
-      <c r="J116" s="106" t="s">
+      <c r="J116" s="112" t="s">
         <v>439</v>
       </c>
-      <c r="K116" s="82" t="s">
+      <c r="K116" s="24" t="s">
         <v>440</v>
       </c>
-      <c r="L116" s="41"/>
+      <c r="L116" s="10"/>
     </row>
     <row r="117" ht="18.3" spans="1:12">
-      <c r="A117" s="90" t="s">
+      <c r="A117" s="109" t="s">
         <v>441</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="C117" s="12" t="s">
+      <c r="C117" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="D117" s="27" t="s">
+      <c r="D117" s="37" t="s">
         <v>443</v>
       </c>
-      <c r="E117" s="95"/>
-      <c r="F117" s="43" t="s">
+      <c r="E117" s="100"/>
+      <c r="F117" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G117" s="19"/>
-      <c r="H117" s="96"/>
-      <c r="I117" s="107" t="s">
+      <c r="G117" s="9"/>
+      <c r="H117" s="101"/>
+      <c r="I117" s="121" t="s">
         <v>438</v>
       </c>
-      <c r="J117" s="108" t="s">
+      <c r="J117" s="122" t="s">
         <v>444</v>
       </c>
-      <c r="K117" s="109" t="s">
+      <c r="K117" s="123" t="s">
         <v>440</v>
       </c>
-      <c r="L117" s="41"/>
+      <c r="L117" s="10"/>
     </row>
     <row r="118" ht="18.3" spans="1:12">
-      <c r="A118" s="90"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="27" t="s">
+      <c r="A118" s="109"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="37" t="s">
         <v>445</v>
       </c>
-      <c r="E118" s="95"/>
-      <c r="F118" s="97" t="s">
+      <c r="E118" s="100"/>
+      <c r="F118" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G118" s="19"/>
-      <c r="H118" s="98" t="s">
+      <c r="G118" s="9"/>
+      <c r="H118" s="111" t="s">
         <v>342</v>
       </c>
-      <c r="I118" s="106" t="s">
+      <c r="I118" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J118" s="106" t="s">
+      <c r="J118" s="112" t="s">
         <v>446</v>
       </c>
-      <c r="K118" s="82" t="s">
+      <c r="K118" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L118" s="41"/>
+      <c r="L118" s="10"/>
     </row>
     <row r="119" ht="18.3" spans="1:12">
-      <c r="A119" s="90"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="12" t="s">
+      <c r="A119" s="109"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="D119" s="27" t="s">
+      <c r="D119" s="37" t="s">
         <v>447</v>
       </c>
-      <c r="E119" s="95"/>
-      <c r="F119" s="97" t="s">
+      <c r="E119" s="100"/>
+      <c r="F119" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G119" s="19"/>
-      <c r="H119" s="98"/>
-      <c r="I119" s="106" t="s">
+      <c r="G119" s="9"/>
+      <c r="H119" s="111"/>
+      <c r="I119" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J119" s="106" t="s">
+      <c r="J119" s="112" t="s">
         <v>448</v>
       </c>
-      <c r="K119" s="82" t="s">
+      <c r="K119" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L119" s="41"/>
+      <c r="L119" s="10"/>
     </row>
     <row r="120" ht="18.3" spans="1:12">
-      <c r="A120" s="90"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="27" t="s">
+      <c r="A120" s="109"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="E120" s="95"/>
-      <c r="F120" s="97" t="s">
+      <c r="E120" s="100"/>
+      <c r="F120" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G120" s="19"/>
-      <c r="H120" s="98"/>
-      <c r="I120" s="106" t="s">
+      <c r="G120" s="9"/>
+      <c r="H120" s="111"/>
+      <c r="I120" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J120" s="106" t="s">
+      <c r="J120" s="112" t="s">
         <v>450</v>
       </c>
-      <c r="K120" s="82" t="s">
+      <c r="K120" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L120" s="41"/>
+      <c r="L120" s="10"/>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:12">
-      <c r="A121" s="90"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="12" t="s">
+      <c r="A121" s="109"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="D121" s="27" t="s">
+      <c r="D121" s="37" t="s">
         <v>451</v>
       </c>
-      <c r="E121" s="95"/>
-      <c r="F121" s="97" t="s">
+      <c r="E121" s="100"/>
+      <c r="F121" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G121" s="19"/>
-      <c r="H121" s="98"/>
-      <c r="I121" s="106" t="s">
+      <c r="G121" s="9"/>
+      <c r="H121" s="111"/>
+      <c r="I121" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J121" s="106" t="s">
+      <c r="J121" s="112" t="s">
         <v>452</v>
       </c>
-      <c r="K121" s="82" t="s">
+      <c r="K121" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L121" s="41"/>
+      <c r="L121" s="10"/>
     </row>
     <row r="122" ht="16" customHeight="1" spans="1:12">
-      <c r="A122" s="90"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="27" t="s">
+      <c r="A122" s="109"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="37" t="s">
         <v>453</v>
       </c>
-      <c r="E122" s="95"/>
-      <c r="F122" s="97" t="s">
+      <c r="E122" s="100"/>
+      <c r="F122" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G122" s="19"/>
-      <c r="H122" s="98"/>
-      <c r="I122" s="106" t="s">
+      <c r="G122" s="9"/>
+      <c r="H122" s="111"/>
+      <c r="I122" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J122" s="106" t="s">
+      <c r="J122" s="112" t="s">
         <v>454</v>
       </c>
-      <c r="K122" s="82" t="s">
+      <c r="K122" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L122" s="41"/>
+      <c r="L122" s="10"/>
     </row>
     <row r="123" ht="16" customHeight="1" spans="1:12">
-      <c r="A123" s="90"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="27" t="s">
+      <c r="A123" s="109"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="37" t="s">
         <v>455</v>
       </c>
-      <c r="E123" s="95"/>
-      <c r="F123" s="97" t="s">
+      <c r="E123" s="100"/>
+      <c r="F123" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="G123" s="19"/>
-      <c r="H123" s="98"/>
-      <c r="I123" s="106" t="s">
+      <c r="G123" s="9"/>
+      <c r="H123" s="111"/>
+      <c r="I123" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J123" s="106" t="s">
+      <c r="J123" s="112" t="s">
         <v>456</v>
       </c>
-      <c r="K123" s="82" t="s">
+      <c r="K123" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L123" s="41"/>
+      <c r="L123" s="10"/>
     </row>
     <row r="124" ht="18.3" spans="1:12">
-      <c r="A124" s="90"/>
-      <c r="B124" s="11" t="s">
+      <c r="A124" s="109"/>
+      <c r="B124" s="25" t="s">
         <v>457</v>
       </c>
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="45" t="s">
         <v>381</v>
       </c>
-      <c r="D124" s="27" t="s">
+      <c r="D124" s="37" t="s">
         <v>458</v>
       </c>
-      <c r="E124" s="95"/>
-      <c r="F124" s="43" t="s">
+      <c r="E124" s="100"/>
+      <c r="F124" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G124" s="19"/>
-      <c r="H124" s="98"/>
-      <c r="I124" s="106" t="s">
+      <c r="G124" s="9"/>
+      <c r="H124" s="111"/>
+      <c r="I124" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J124" s="106" t="s">
+      <c r="J124" s="112" t="s">
         <v>459</v>
       </c>
-      <c r="K124" s="82" t="s">
+      <c r="K124" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L124" s="41"/>
+      <c r="L124" s="10"/>
     </row>
     <row r="125" ht="18.3" spans="1:12">
-      <c r="A125" s="90"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="27" t="s">
+      <c r="A125" s="109"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="37" t="s">
         <v>460</v>
       </c>
-      <c r="E125" s="95"/>
-      <c r="F125" s="97" t="s">
+      <c r="E125" s="100"/>
+      <c r="F125" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G125" s="19"/>
-      <c r="H125" s="98"/>
-      <c r="I125" s="106" t="s">
+      <c r="G125" s="9"/>
+      <c r="H125" s="111"/>
+      <c r="I125" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J125" s="106" t="s">
+      <c r="J125" s="112" t="s">
         <v>461</v>
       </c>
-      <c r="K125" s="82" t="s">
+      <c r="K125" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L125" s="41"/>
+      <c r="L125" s="10"/>
     </row>
     <row r="126" ht="18.3" spans="1:12">
-      <c r="A126" s="90"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="15" t="s">
+      <c r="A126" s="109"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="45" t="s">
         <v>392</v>
       </c>
-      <c r="D126" s="91" t="s">
+      <c r="D126" s="116" t="s">
         <v>462</v>
       </c>
-      <c r="E126" s="95"/>
-      <c r="F126" s="97" t="s">
+      <c r="E126" s="100"/>
+      <c r="F126" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G126" s="19"/>
-      <c r="H126" s="98"/>
-      <c r="I126" s="106" t="s">
+      <c r="G126" s="9"/>
+      <c r="H126" s="111"/>
+      <c r="I126" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J126" s="106" t="s">
+      <c r="J126" s="112" t="s">
         <v>463</v>
       </c>
-      <c r="K126" s="82" t="s">
+      <c r="K126" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="L126" s="41"/>
+      <c r="L126" s="10"/>
     </row>
     <row r="127" ht="18.3" spans="1:12">
-      <c r="A127" s="90"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="91" t="s">
+      <c r="A127" s="109"/>
+      <c r="B127" s="25"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="116" t="s">
         <v>464</v>
       </c>
-      <c r="E127" s="95"/>
-      <c r="F127" s="97" t="s">
+      <c r="E127" s="100"/>
+      <c r="F127" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G127" s="19"/>
-      <c r="H127" s="98"/>
-      <c r="I127" s="106" t="s">
+      <c r="G127" s="9"/>
+      <c r="H127" s="111"/>
+      <c r="I127" s="112" t="s">
         <v>343</v>
       </c>
-      <c r="J127" s="106" t="s">
+      <c r="J127" s="112" t="s">
         <v>465</v>
       </c>
-      <c r="K127" s="82" t="s">
+      <c r="K127" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="L127" s="41"/>
+      <c r="L127" s="10"/>
     </row>
     <row r="128" ht="18.3" spans="1:12">
-      <c r="A128" s="90"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="15" t="s">
+      <c r="A128" s="109"/>
+      <c r="B128" s="25"/>
+      <c r="C128" s="45" t="s">
         <v>403</v>
       </c>
-      <c r="D128" s="91" t="s">
+      <c r="D128" s="116" t="s">
         <v>466</v>
       </c>
-      <c r="E128" s="95"/>
-      <c r="F128" s="97" t="s">
+      <c r="E128" s="100"/>
+      <c r="F128" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G128" s="19"/>
-      <c r="H128" s="98"/>
-      <c r="I128" s="106" t="s">
+      <c r="G128" s="9"/>
+      <c r="H128" s="111"/>
+      <c r="I128" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J128" s="106" t="s">
+      <c r="J128" s="112" t="s">
         <v>467</v>
       </c>
-      <c r="K128" s="82" t="s">
+      <c r="K128" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L128" s="41"/>
+      <c r="L128" s="10"/>
     </row>
     <row r="129" ht="18.3" spans="1:12">
-      <c r="A129" s="90"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="91" t="s">
+      <c r="A129" s="109"/>
+      <c r="B129" s="25"/>
+      <c r="C129" s="45"/>
+      <c r="D129" s="116" t="s">
         <v>468</v>
       </c>
-      <c r="E129" s="95"/>
-      <c r="F129" s="97" t="s">
+      <c r="E129" s="100"/>
+      <c r="F129" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G129" s="19"/>
-      <c r="H129" s="98"/>
-      <c r="I129" s="106" t="s">
+      <c r="G129" s="9"/>
+      <c r="H129" s="111"/>
+      <c r="I129" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J129" s="106" t="s">
+      <c r="J129" s="112" t="s">
         <v>469</v>
       </c>
-      <c r="K129" s="82" t="s">
+      <c r="K129" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L129" s="41"/>
+      <c r="L129" s="10"/>
     </row>
     <row r="130" ht="18.3" spans="1:12">
-      <c r="A130" s="90"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="15"/>
-      <c r="D130" s="91" t="s">
+      <c r="A130" s="109"/>
+      <c r="B130" s="25"/>
+      <c r="C130" s="45"/>
+      <c r="D130" s="116" t="s">
         <v>470</v>
       </c>
-      <c r="E130" s="95"/>
-      <c r="F130" s="97" t="s">
+      <c r="E130" s="100"/>
+      <c r="F130" s="110" t="s">
         <v>375</v>
       </c>
-      <c r="G130" s="19"/>
-      <c r="H130" s="98"/>
-      <c r="I130" s="106" t="s">
+      <c r="G130" s="9"/>
+      <c r="H130" s="111"/>
+      <c r="I130" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J130" s="106" t="s">
+      <c r="J130" s="112" t="s">
         <v>471</v>
       </c>
-      <c r="K130" s="82" t="s">
+      <c r="K130" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L130" s="41"/>
+      <c r="L130" s="10"/>
     </row>
     <row r="131" ht="18.3" spans="1:12">
-      <c r="A131" s="90"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="15" t="s">
+      <c r="A131" s="109"/>
+      <c r="B131" s="25"/>
+      <c r="C131" s="45" t="s">
         <v>417</v>
       </c>
-      <c r="D131" s="91" t="s">
+      <c r="D131" s="116" t="s">
         <v>472</v>
       </c>
-      <c r="E131" s="95"/>
-      <c r="F131" s="43" t="s">
+      <c r="E131" s="100"/>
+      <c r="F131" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="G131" s="19"/>
-      <c r="H131" s="98"/>
-      <c r="I131" s="106" t="s">
+      <c r="G131" s="9"/>
+      <c r="H131" s="111"/>
+      <c r="I131" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J131" s="106" t="s">
+      <c r="J131" s="112" t="s">
         <v>473</v>
       </c>
-      <c r="K131" s="82" t="s">
+      <c r="K131" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L131" s="41"/>
+      <c r="L131" s="10"/>
     </row>
     <row r="132" ht="18.3" spans="1:12">
-      <c r="A132" s="90"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="91" t="s">
+      <c r="A132" s="109"/>
+      <c r="B132" s="25"/>
+      <c r="C132" s="26"/>
+      <c r="D132" s="116" t="s">
         <v>474</v>
       </c>
-      <c r="E132" s="95"/>
-      <c r="F132" s="97" t="s">
+      <c r="E132" s="100"/>
+      <c r="F132" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="G132" s="19"/>
-      <c r="H132" s="98"/>
-      <c r="I132" s="106" t="s">
+      <c r="G132" s="9"/>
+      <c r="H132" s="111"/>
+      <c r="I132" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J132" s="106" t="s">
+      <c r="J132" s="112" t="s">
         <v>475</v>
       </c>
-      <c r="K132" s="82" t="s">
+      <c r="K132" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="L132" s="41"/>
+      <c r="L132" s="10"/>
     </row>
     <row r="133" ht="18.3" spans="1:12">
-      <c r="A133" s="90"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="15" t="s">
+      <c r="A133" s="109"/>
+      <c r="B133" s="25"/>
+      <c r="C133" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="D133" s="91" t="s">
+      <c r="D133" s="116" t="s">
         <v>476</v>
       </c>
-      <c r="E133" s="95"/>
-      <c r="F133" s="97" t="s">
+      <c r="E133" s="100"/>
+      <c r="F133" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="G133" s="19"/>
-      <c r="H133" s="98"/>
-      <c r="I133" s="106" t="s">
+      <c r="G133" s="9"/>
+      <c r="H133" s="111"/>
+      <c r="I133" s="112" t="s">
         <v>405</v>
       </c>
-      <c r="J133" s="106" t="s">
+      <c r="J133" s="112" t="s">
         <v>477</v>
       </c>
-      <c r="K133" s="82" t="s">
+      <c r="K133" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="L133" s="41"/>
+      <c r="L133" s="10"/>
     </row>
     <row r="134" ht="18.3" spans="1:12">
-      <c r="A134" s="90"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="91" t="s">
+      <c r="A134" s="109"/>
+      <c r="B134" s="25"/>
+      <c r="C134" s="26"/>
+      <c r="D134" s="116" t="s">
         <v>478</v>
       </c>
-      <c r="E134" s="95"/>
-      <c r="F134" s="97" t="s">
+      <c r="E134" s="100"/>
+      <c r="F134" s="110" t="s">
         <v>356</v>
       </c>
-      <c r="G134" s="19"/>
-      <c r="H134" s="98"/>
-      <c r="I134" s="106" t="s">
+      <c r="G134" s="9"/>
+      <c r="H134" s="111"/>
+      <c r="I134" s="112" t="s">
         <v>426</v>
       </c>
-      <c r="J134" s="106" t="s">
+      <c r="J134" s="112" t="s">
         <v>479</v>
       </c>
-      <c r="K134" s="82" t="s">
+      <c r="K134" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="L134" s="41"/>
+      <c r="L134" s="10"/>
     </row>
     <row r="135" ht="18.3" spans="1:12">
-      <c r="A135" s="90"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="15" t="s">
+      <c r="A135" s="109"/>
+      <c r="B135" s="25"/>
+      <c r="C135" s="45" t="s">
         <v>428</v>
       </c>
-      <c r="D135" s="91" t="s">
+      <c r="D135" s="116" t="s">
         <v>480</v>
       </c>
-      <c r="E135" s="95"/>
-      <c r="F135" s="97" t="s">
+      <c r="E135" s="100"/>
+      <c r="F135" s="110" t="s">
         <v>363</v>
       </c>
-      <c r="G135" s="19"/>
-      <c r="H135" s="98"/>
-      <c r="I135" s="106" t="s">
+      <c r="G135" s="9"/>
+      <c r="H135" s="111"/>
+      <c r="I135" s="112" t="s">
         <v>426</v>
       </c>
-      <c r="J135" s="106" t="s">
+      <c r="J135" s="112" t="s">
         <v>481</v>
       </c>
-      <c r="K135" s="82" t="s">
+      <c r="K135" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="L135" s="41"/>
+      <c r="L135" s="10"/>
     </row>
     <row r="136" ht="18.3" spans="1:12">
-      <c r="A136" s="90"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="15"/>
-      <c r="D136" s="91" t="s">
+      <c r="A136" s="109"/>
+      <c r="B136" s="25"/>
+      <c r="C136" s="45"/>
+      <c r="D136" s="116" t="s">
         <v>482</v>
       </c>
-      <c r="E136" s="95"/>
-      <c r="F136" s="97" t="s">
+      <c r="E136" s="100"/>
+      <c r="F136" s="110" t="s">
         <v>369</v>
       </c>
-      <c r="G136" s="19"/>
-      <c r="H136" s="99" t="s">
+      <c r="G136" s="9"/>
+      <c r="H136" s="119" t="s">
         <v>432</v>
       </c>
-      <c r="I136" s="106" t="s">
+      <c r="I136" s="112" t="s">
         <v>433</v>
       </c>
-      <c r="J136" s="106" t="s">
+      <c r="J136" s="112" t="s">
         <v>483</v>
       </c>
-      <c r="K136" s="82" t="s">
+      <c r="K136" s="24" t="s">
         <v>435</v>
       </c>
-      <c r="L136" s="41"/>
+      <c r="L136" s="10"/>
     </row>
     <row r="137" ht="18.3" spans="1:12">
-      <c r="A137" s="90"/>
+      <c r="A137" s="109"/>
       <c r="B137" s="86"/>
       <c r="C137" s="124"/>
-      <c r="D137" s="111" t="s">
+      <c r="D137" s="96" t="s">
         <v>484</v>
       </c>
-      <c r="E137" s="121"/>
+      <c r="E137" s="118"/>
       <c r="F137" s="125" t="s">
         <v>375</v>
       </c>
-      <c r="G137" s="19"/>
+      <c r="G137" s="9"/>
       <c r="H137" s="126" t="s">
         <v>437</v>
       </c>
@@ -13866,9 +13878,9 @@
       <c r="K137" s="128" t="s">
         <v>440</v>
       </c>
-      <c r="L137" s="41"/>
+      <c r="L137" s="10"/>
     </row>
-    <row r="138" ht="17.55" spans="8:8">
+    <row r="138" ht="17.55" spans="1:12">
       <c r="H138" s="3"/>
     </row>
   </sheetData>
